--- a/research/traditional_assets/database/data/philippines/philippines_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_environmental_waste_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1010704306027203</v>
+        <v>0.1008515045262135</v>
       </c>
       <c r="C2">
-        <v>36.07177070260736</v>
+        <v>35.84970609047923</v>
       </c>
       <c r="D2">
-        <v>34.91177070260736</v>
+        <v>35.05060609047923</v>
       </c>
       <c r="E2">
-        <v>-0.49</v>
+        <v>-0.1290999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3609000000000001</v>
       </c>
       <c r="G2">
         <v>1.16</v>
@@ -1445,28 +1445,28 @@
         <v>1.48</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01815327</v>
       </c>
       <c r="N2">
-        <v>1.48</v>
+        <v>1.46184673</v>
       </c>
       <c r="O2">
-        <v>0.37</v>
+        <v>0.3654616825</v>
       </c>
       <c r="P2">
-        <v>1.11</v>
+        <v>1.0963850475</v>
       </c>
       <c r="Q2">
-        <v>1.65</v>
+        <v>1.6363850475</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1010704306027203</v>
+        <v>0.1014891459860743</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8103449292580148</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>81.52801120679634</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1008515045262135</v>
+        <v>0.1006325784497067</v>
       </c>
       <c r="C3">
-        <v>35.84970609047923</v>
+        <v>35.62875011440676</v>
       </c>
       <c r="D3">
-        <v>35.05060609047923</v>
+        <v>35.19055011440677</v>
       </c>
       <c r="E3">
-        <v>-0.1290999999999999</v>
+        <v>0.2318000000000001</v>
       </c>
       <c r="F3">
-        <v>0.3609000000000001</v>
+        <v>0.7218000000000001</v>
       </c>
       <c r="G3">
         <v>1.16</v>
@@ -1527,28 +1527,28 @@
         <v>1.48</v>
       </c>
       <c r="M3">
-        <v>0.01815327</v>
+        <v>0.03630654000000001</v>
       </c>
       <c r="N3">
-        <v>1.46184673</v>
+        <v>1.44369346</v>
       </c>
       <c r="O3">
-        <v>0.3654616825</v>
+        <v>0.360923365</v>
       </c>
       <c r="P3">
-        <v>1.0963850475</v>
+        <v>1.082770095</v>
       </c>
       <c r="Q3">
-        <v>1.6363850475</v>
+        <v>1.622770095</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1014891459860743</v>
+        <v>0.1019164065813334</v>
       </c>
       <c r="T3">
-        <v>0.8103449292580148</v>
+        <v>0.8165620915202368</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>81.52801120679634</v>
+        <v>40.76400560339817</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1006325784497067</v>
+        <v>0.1004136523731999</v>
       </c>
       <c r="C4">
-        <v>35.62875011440676</v>
+        <v>35.40891610673442</v>
       </c>
       <c r="D4">
-        <v>35.19055011440677</v>
+        <v>35.33161610673443</v>
       </c>
       <c r="E4">
-        <v>0.2318000000000001</v>
+        <v>0.5927</v>
       </c>
       <c r="F4">
-        <v>0.7218000000000001</v>
+        <v>1.0827</v>
       </c>
       <c r="G4">
         <v>1.16</v>
@@ -1609,28 +1609,28 @@
         <v>1.48</v>
       </c>
       <c r="M4">
-        <v>0.03630654000000001</v>
+        <v>0.05445981</v>
       </c>
       <c r="N4">
-        <v>1.44369346</v>
+        <v>1.42554019</v>
       </c>
       <c r="O4">
-        <v>0.360923365</v>
+        <v>0.3563850475</v>
       </c>
       <c r="P4">
-        <v>1.082770095</v>
+        <v>1.0691551425</v>
       </c>
       <c r="Q4">
-        <v>1.622770095</v>
+        <v>1.6091551425</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1019164065813334</v>
+        <v>0.102352476673402</v>
       </c>
       <c r="T4">
-        <v>0.8165620915202368</v>
+        <v>0.8229074426950819</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>40.76400560339817</v>
+        <v>27.17600373559878</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1004136523731999</v>
+        <v>0.1001947262966931</v>
       </c>
       <c r="C5">
-        <v>35.40891610673442</v>
+        <v>35.19021761444496</v>
       </c>
       <c r="D5">
-        <v>35.33161610673443</v>
+        <v>35.47381761444497</v>
       </c>
       <c r="E5">
-        <v>0.5927</v>
+        <v>0.9536000000000002</v>
       </c>
       <c r="F5">
-        <v>1.0827</v>
+        <v>1.4436</v>
       </c>
       <c r="G5">
         <v>1.16</v>
@@ -1691,28 +1691,28 @@
         <v>1.48</v>
       </c>
       <c r="M5">
-        <v>0.05445981</v>
+        <v>0.07261308000000001</v>
       </c>
       <c r="N5">
-        <v>1.42554019</v>
+        <v>1.40738692</v>
       </c>
       <c r="O5">
-        <v>0.3563850475</v>
+        <v>0.35184673</v>
       </c>
       <c r="P5">
-        <v>1.0691551425</v>
+        <v>1.05554019</v>
       </c>
       <c r="Q5">
-        <v>1.6091551425</v>
+        <v>1.59554019</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.102352476673402</v>
+        <v>0.1027976315590553</v>
       </c>
       <c r="T5">
-        <v>0.8229074426950819</v>
+        <v>0.8293849886860697</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.17600373559878</v>
+        <v>20.38200280169908</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1001947262966931</v>
+        <v>0.09997580022018633</v>
       </c>
       <c r="C6">
-        <v>35.19021761444496</v>
+        <v>34.97266840349624</v>
       </c>
       <c r="D6">
-        <v>35.47381761444497</v>
+        <v>35.61716840349624</v>
       </c>
       <c r="E6">
-        <v>0.9536000000000002</v>
+        <v>1.3145</v>
       </c>
       <c r="F6">
-        <v>1.4436</v>
+        <v>1.8045</v>
       </c>
       <c r="G6">
         <v>1.16</v>
@@ -1773,28 +1773,28 @@
         <v>1.48</v>
       </c>
       <c r="M6">
-        <v>0.07261308000000001</v>
+        <v>0.09076635000000001</v>
       </c>
       <c r="N6">
-        <v>1.40738692</v>
+        <v>1.38923365</v>
       </c>
       <c r="O6">
-        <v>0.35184673</v>
+        <v>0.3473084125</v>
       </c>
       <c r="P6">
-        <v>1.05554019</v>
+        <v>1.0419252375</v>
       </c>
       <c r="Q6">
-        <v>1.59554019</v>
+        <v>1.5819252375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1027976315590553</v>
+        <v>0.1032521581265119</v>
       </c>
       <c r="T6">
-        <v>0.8293849886860697</v>
+        <v>0.8359989040663414</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.38200280169908</v>
+        <v>16.30560224135927</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09997580022018633</v>
+        <v>0.09975687414367952</v>
       </c>
       <c r="C7">
-        <v>34.97266840349624</v>
+        <v>34.7562824632636</v>
       </c>
       <c r="D7">
-        <v>35.61716840349624</v>
+        <v>35.7616824632636</v>
       </c>
       <c r="E7">
-        <v>1.3145</v>
+        <v>1.6754</v>
       </c>
       <c r="F7">
-        <v>1.8045</v>
+        <v>2.1654</v>
       </c>
       <c r="G7">
         <v>1.16</v>
@@ -1855,28 +1855,28 @@
         <v>1.48</v>
       </c>
       <c r="M7">
-        <v>0.09076635000000001</v>
+        <v>0.10891962</v>
       </c>
       <c r="N7">
-        <v>1.38923365</v>
+        <v>1.37108038</v>
       </c>
       <c r="O7">
-        <v>0.3473084125</v>
+        <v>0.342770095</v>
       </c>
       <c r="P7">
-        <v>1.0419252375</v>
+        <v>1.028310285</v>
       </c>
       <c r="Q7">
-        <v>1.5819252375</v>
+        <v>1.568310285</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1032521581265119</v>
+        <v>0.1037163554719995</v>
       </c>
       <c r="T7">
-        <v>0.8359989040663414</v>
+        <v>0.8427535410504486</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.30560224135927</v>
+        <v>13.58800186779939</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09975687414367952</v>
+        <v>0.09961669806717272</v>
       </c>
       <c r="C8">
-        <v>34.7562824632636</v>
+        <v>34.48853073354071</v>
       </c>
       <c r="D8">
-        <v>35.7616824632636</v>
+        <v>35.85483073354071</v>
       </c>
       <c r="E8">
-        <v>1.6754</v>
+        <v>2.0363</v>
       </c>
       <c r="F8">
-        <v>2.1654</v>
+        <v>2.5263</v>
       </c>
       <c r="G8">
         <v>1.16</v>
@@ -1937,45 +1937,45 @@
         <v>1.48</v>
       </c>
       <c r="M8">
-        <v>0.10891962</v>
+        <v>0.13086234</v>
       </c>
       <c r="N8">
-        <v>1.37108038</v>
+        <v>1.34913766</v>
       </c>
       <c r="O8">
-        <v>0.342770095</v>
+        <v>0.337284415</v>
       </c>
       <c r="P8">
-        <v>1.028310285</v>
+        <v>1.011853245</v>
       </c>
       <c r="Q8">
-        <v>1.568310285</v>
+        <v>1.551853245</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1037163554719995</v>
+        <v>0.1041905355560997</v>
       </c>
       <c r="T8">
-        <v>0.8427535410504486</v>
+        <v>0.8496534390449667</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.58800186779939</v>
+        <v>11.3095944944894</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09961669806717272</v>
+        <v>0.09940902199066592</v>
       </c>
       <c r="C9">
-        <v>34.48853073354071</v>
+        <v>34.26652881998319</v>
       </c>
       <c r="D9">
-        <v>35.85483073354071</v>
+        <v>35.9937288199832</v>
       </c>
       <c r="E9">
-        <v>2.036300000000001</v>
+        <v>2.397200000000001</v>
       </c>
       <c r="F9">
-        <v>2.5263</v>
+        <v>2.8872</v>
       </c>
       <c r="G9">
         <v>1.16</v>
@@ -2019,28 +2019,28 @@
         <v>1.48</v>
       </c>
       <c r="M9">
-        <v>0.13086234</v>
+        <v>0.14955696</v>
       </c>
       <c r="N9">
-        <v>1.34913766</v>
+        <v>1.33044304</v>
       </c>
       <c r="O9">
-        <v>0.337284415</v>
+        <v>0.33261076</v>
       </c>
       <c r="P9">
-        <v>1.011853245</v>
+        <v>0.99783228</v>
       </c>
       <c r="Q9">
-        <v>1.551853245</v>
+        <v>1.53783228</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1041905355560997</v>
+        <v>0.1046750239028977</v>
       </c>
       <c r="T9">
-        <v>0.8496534390449667</v>
+        <v>0.8567033348219746</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.3095944944894</v>
+        <v>9.895895182678224</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09940902199066592</v>
+        <v>0.09931609591415912</v>
       </c>
       <c r="C10">
-        <v>34.26652881998319</v>
+        <v>33.96812882004777</v>
       </c>
       <c r="D10">
-        <v>35.9937288199832</v>
+        <v>36.05622882004778</v>
       </c>
       <c r="E10">
-        <v>2.397200000000001</v>
+        <v>2.7581</v>
       </c>
       <c r="F10">
-        <v>2.8872</v>
+        <v>3.2481</v>
       </c>
       <c r="G10">
         <v>1.16</v>
@@ -2101,45 +2101,45 @@
         <v>1.48</v>
       </c>
       <c r="M10">
-        <v>0.14955696</v>
+        <v>0.17377335</v>
       </c>
       <c r="N10">
-        <v>1.33044304</v>
+        <v>1.30622665</v>
       </c>
       <c r="O10">
-        <v>0.33261076</v>
+        <v>0.3265566625</v>
       </c>
       <c r="P10">
-        <v>0.99783228</v>
+        <v>0.9796699874999999</v>
       </c>
       <c r="Q10">
-        <v>1.53783228</v>
+        <v>1.5196699875</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1046750239028977</v>
+        <v>0.1051701603452298</v>
       </c>
       <c r="T10">
-        <v>0.8567033348219746</v>
+        <v>0.8639081733633119</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>9.895895182678224</v>
+        <v>8.516841046109775</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09931609591415912</v>
+        <v>0.09912116983765232</v>
       </c>
       <c r="C11">
-        <v>33.96812882004777</v>
+        <v>33.73903949184891</v>
       </c>
       <c r="D11">
-        <v>36.05622882004778</v>
+        <v>36.18803949184891</v>
       </c>
       <c r="E11">
-        <v>2.7581</v>
+        <v>3.119</v>
       </c>
       <c r="F11">
-        <v>3.2481</v>
+        <v>3.609</v>
       </c>
       <c r="G11">
         <v>1.16</v>
@@ -2183,28 +2183,28 @@
         <v>1.48</v>
       </c>
       <c r="M11">
-        <v>0.17377335</v>
+        <v>0.1930815</v>
       </c>
       <c r="N11">
-        <v>1.30622665</v>
+        <v>1.2869185</v>
       </c>
       <c r="O11">
-        <v>0.3265566625</v>
+        <v>0.321729625</v>
       </c>
       <c r="P11">
-        <v>0.9796699874999999</v>
+        <v>0.9651888750000001</v>
       </c>
       <c r="Q11">
-        <v>1.5196699875</v>
+        <v>1.505188875</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1051701603452298</v>
+        <v>0.1056762998196137</v>
       </c>
       <c r="T11">
-        <v>0.8639081733633119</v>
+        <v>0.8712731194277903</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.516841046109775</v>
+        <v>7.665156941498798</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09912116983765232</v>
+        <v>0.09899224376114552</v>
       </c>
       <c r="C12">
-        <v>33.73903949184891</v>
+        <v>33.46585118848474</v>
       </c>
       <c r="D12">
-        <v>36.18803949184891</v>
+        <v>36.27575118848475</v>
       </c>
       <c r="E12">
-        <v>3.119000000000001</v>
+        <v>3.479900000000001</v>
       </c>
       <c r="F12">
-        <v>3.609</v>
+        <v>3.9699</v>
       </c>
       <c r="G12">
         <v>1.16</v>
@@ -2265,45 +2265,45 @@
         <v>1.48</v>
       </c>
       <c r="M12">
-        <v>0.1930815</v>
+        <v>0.21556557</v>
       </c>
       <c r="N12">
-        <v>1.2869185</v>
+        <v>1.26443443</v>
       </c>
       <c r="O12">
-        <v>0.321729625</v>
+        <v>0.3161086075</v>
       </c>
       <c r="P12">
-        <v>0.9651888750000001</v>
+        <v>0.9483258225</v>
       </c>
       <c r="Q12">
-        <v>1.505188875</v>
+        <v>1.4883258225</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1056762998196137</v>
+        <v>0.1061938132147702</v>
       </c>
       <c r="T12">
-        <v>0.8712731194277903</v>
+        <v>0.8788035698982121</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.665156941498797</v>
+        <v>6.865660411354186</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09899224376114552</v>
+        <v>0.09880331768463871</v>
       </c>
       <c r="C13">
-        <v>33.46585118848474</v>
+        <v>33.23425319529787</v>
       </c>
       <c r="D13">
-        <v>36.27575118848475</v>
+        <v>36.40505319529787</v>
       </c>
       <c r="E13">
-        <v>3.479900000000001</v>
+        <v>3.8408</v>
       </c>
       <c r="F13">
-        <v>3.9699</v>
+        <v>4.3308</v>
       </c>
       <c r="G13">
         <v>1.16</v>
@@ -2347,28 +2347,28 @@
         <v>1.48</v>
       </c>
       <c r="M13">
-        <v>0.21556557</v>
+        <v>0.23516244</v>
       </c>
       <c r="N13">
-        <v>1.26443443</v>
+        <v>1.24483756</v>
       </c>
       <c r="O13">
-        <v>0.3161086075</v>
+        <v>0.31120939</v>
       </c>
       <c r="P13">
-        <v>0.9483258225</v>
+        <v>0.93362817</v>
       </c>
       <c r="Q13">
-        <v>1.4883258225</v>
+        <v>1.47362817</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1061938132147702</v>
+        <v>0.1067230882779985</v>
       </c>
       <c r="T13">
-        <v>0.8788035698982121</v>
+        <v>0.8865051669702343</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.865660411354186</v>
+        <v>6.293522043741339</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09880331768463871</v>
+        <v>0.09871189160813192</v>
       </c>
       <c r="C14">
-        <v>33.23425319529787</v>
+        <v>32.936257224572</v>
       </c>
       <c r="D14">
-        <v>36.40505319529787</v>
+        <v>36.467957224572</v>
       </c>
       <c r="E14">
-        <v>3.8408</v>
+        <v>4.201700000000001</v>
       </c>
       <c r="F14">
-        <v>4.3308</v>
+        <v>4.691700000000001</v>
       </c>
       <c r="G14">
         <v>1.16</v>
@@ -2429,45 +2429,45 @@
         <v>1.48</v>
       </c>
       <c r="M14">
-        <v>0.23516244</v>
+        <v>0.25945101</v>
       </c>
       <c r="N14">
-        <v>1.24483756</v>
+        <v>1.22054899</v>
       </c>
       <c r="O14">
-        <v>0.31120939</v>
+        <v>0.3051372475</v>
       </c>
       <c r="P14">
-        <v>0.93362817</v>
+        <v>0.9154117424999999</v>
       </c>
       <c r="Q14">
-        <v>1.47362817</v>
+        <v>1.4554117425</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1067230882779985</v>
+        <v>0.1072645305840597</v>
       </c>
       <c r="T14">
-        <v>0.8865051669702343</v>
+        <v>0.8943838122508087</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.293522043741339</v>
+        <v>5.704352432468849</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09871189160813192</v>
+        <v>0.09853046553162513</v>
       </c>
       <c r="C15">
-        <v>32.936257224572</v>
+        <v>32.7008300101954</v>
       </c>
       <c r="D15">
-        <v>36.467957224572</v>
+        <v>36.5934300101954</v>
       </c>
       <c r="E15">
-        <v>4.201700000000001</v>
+        <v>4.562600000000001</v>
       </c>
       <c r="F15">
-        <v>4.691700000000001</v>
+        <v>5.052600000000001</v>
       </c>
       <c r="G15">
         <v>1.16</v>
@@ -2511,28 +2511,28 @@
         <v>1.48</v>
       </c>
       <c r="M15">
-        <v>0.25945101</v>
+        <v>0.2794087800000001</v>
       </c>
       <c r="N15">
-        <v>1.22054899</v>
+        <v>1.20059122</v>
       </c>
       <c r="O15">
-        <v>0.3051372475</v>
+        <v>0.300147805</v>
       </c>
       <c r="P15">
-        <v>0.9154117424999999</v>
+        <v>0.900443415</v>
       </c>
       <c r="Q15">
-        <v>1.4554117425</v>
+        <v>1.440443415</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1072645305840597</v>
+        <v>0.1078185645716571</v>
       </c>
       <c r="T15">
-        <v>0.8943838122508087</v>
+        <v>0.9024456818402337</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.704352432468849</v>
+        <v>5.296898687292503</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09853046553162513</v>
+        <v>0.09834903945511832</v>
       </c>
       <c r="C16">
-        <v>32.7008300101954</v>
+        <v>32.46626918787621</v>
       </c>
       <c r="D16">
-        <v>36.5934300101954</v>
+        <v>36.71976918787621</v>
       </c>
       <c r="E16">
-        <v>4.562600000000001</v>
+        <v>4.923500000000002</v>
       </c>
       <c r="F16">
-        <v>5.052600000000001</v>
+        <v>5.413500000000002</v>
       </c>
       <c r="G16">
         <v>1.16</v>
@@ -2593,28 +2593,28 @@
         <v>1.48</v>
       </c>
       <c r="M16">
-        <v>0.2794087800000001</v>
+        <v>0.2993665500000001</v>
       </c>
       <c r="N16">
-        <v>1.20059122</v>
+        <v>1.18063345</v>
       </c>
       <c r="O16">
-        <v>0.300147805</v>
+        <v>0.2951583624999999</v>
       </c>
       <c r="P16">
-        <v>0.900443415</v>
+        <v>0.8854750874999998</v>
       </c>
       <c r="Q16">
-        <v>1.440443415</v>
+        <v>1.4254750875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1078185645716571</v>
+        <v>0.1083856346530804</v>
       </c>
       <c r="T16">
-        <v>0.9024456818402337</v>
+        <v>0.9106972424788216</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.296898687292503</v>
+        <v>4.943772108139668</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09834903945511832</v>
+        <v>0.09816761337861152</v>
       </c>
       <c r="C17">
-        <v>32.46626918787621</v>
+        <v>32.23258376238483</v>
       </c>
       <c r="D17">
-        <v>36.71976918787621</v>
+        <v>36.84698376238483</v>
       </c>
       <c r="E17">
-        <v>4.9235</v>
+        <v>5.284400000000001</v>
       </c>
       <c r="F17">
-        <v>5.4135</v>
+        <v>5.774400000000001</v>
       </c>
       <c r="G17">
         <v>1.16</v>
@@ -2675,28 +2675,28 @@
         <v>1.48</v>
       </c>
       <c r="M17">
-        <v>0.29936655</v>
+        <v>0.3193243200000001</v>
       </c>
       <c r="N17">
-        <v>1.18063345</v>
+        <v>1.16067568</v>
       </c>
       <c r="O17">
-        <v>0.2951583625</v>
+        <v>0.29016892</v>
       </c>
       <c r="P17">
-        <v>0.8854750874999999</v>
+        <v>0.87050676</v>
       </c>
       <c r="Q17">
-        <v>1.4254750875</v>
+        <v>1.41050676</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1083856346530804</v>
+        <v>0.1089662064031089</v>
       </c>
       <c r="T17">
-        <v>0.9106972424788216</v>
+        <v>0.9191452688468997</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.943772108139671</v>
+        <v>4.63478635138094</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09816761337861152</v>
+        <v>0.09830493730210471</v>
       </c>
       <c r="C18">
-        <v>32.23258376238483</v>
+        <v>31.77531239924946</v>
       </c>
       <c r="D18">
-        <v>36.84698376238483</v>
+        <v>36.75061239924946</v>
       </c>
       <c r="E18">
-        <v>5.284400000000001</v>
+        <v>5.645300000000001</v>
       </c>
       <c r="F18">
-        <v>5.774400000000001</v>
+        <v>6.135300000000001</v>
       </c>
       <c r="G18">
         <v>1.16</v>
@@ -2757,45 +2757,45 @@
         <v>1.48</v>
       </c>
       <c r="M18">
-        <v>0.3193243200000001</v>
+        <v>0.3546203400000001</v>
       </c>
       <c r="N18">
-        <v>1.16067568</v>
+        <v>1.12537966</v>
       </c>
       <c r="O18">
-        <v>0.29016892</v>
+        <v>0.281344915</v>
       </c>
       <c r="P18">
-        <v>0.87050676</v>
+        <v>0.8440347449999999</v>
       </c>
       <c r="Q18">
-        <v>1.41050676</v>
+        <v>1.384034745</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1089662064031089</v>
+        <v>0.1095607678338611</v>
       </c>
       <c r="T18">
-        <v>0.9191452688468997</v>
+        <v>0.9277968621154136</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.63478635138094</v>
+        <v>4.173477471709603</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09830493730210471</v>
+        <v>0.09861476122559791</v>
       </c>
       <c r="C19">
-        <v>31.77531239924946</v>
+        <v>31.19882458515944</v>
       </c>
       <c r="D19">
-        <v>36.75061239924946</v>
+        <v>36.53502458515944</v>
       </c>
       <c r="E19">
-        <v>5.645300000000001</v>
+        <v>6.006200000000002</v>
       </c>
       <c r="F19">
-        <v>6.135300000000001</v>
+        <v>6.496200000000002</v>
       </c>
       <c r="G19">
         <v>1.16</v>
@@ -2839,45 +2839,45 @@
         <v>1.48</v>
       </c>
       <c r="M19">
-        <v>0.3546203400000001</v>
+        <v>0.3982170600000001</v>
       </c>
       <c r="N19">
-        <v>1.12537966</v>
+        <v>1.08178294</v>
       </c>
       <c r="O19">
-        <v>0.281344915</v>
+        <v>0.270445735</v>
       </c>
       <c r="P19">
-        <v>0.8440347449999999</v>
+        <v>0.8113372049999998</v>
       </c>
       <c r="Q19">
-        <v>1.384034745</v>
+        <v>1.351337205</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1095607678338611</v>
+        <v>0.1101698307629243</v>
       </c>
       <c r="T19">
-        <v>0.9277968621154136</v>
+        <v>0.9366594698538909</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.173477471709603</v>
+        <v>3.716566035618865</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09861476122559792</v>
+        <v>0.09847833514909113</v>
       </c>
       <c r="C20">
-        <v>31.19882458515942</v>
+        <v>30.93254280050594</v>
       </c>
       <c r="D20">
-        <v>36.53502458515943</v>
+        <v>36.62964280050594</v>
       </c>
       <c r="E20">
-        <v>6.0062</v>
+        <v>6.367100000000001</v>
       </c>
       <c r="F20">
-        <v>6.4962</v>
+        <v>6.857100000000001</v>
       </c>
       <c r="G20">
         <v>1.16</v>
@@ -2921,28 +2921,28 @@
         <v>1.48</v>
       </c>
       <c r="M20">
-        <v>0.39821706</v>
+        <v>0.42034023</v>
       </c>
       <c r="N20">
-        <v>1.08178294</v>
+        <v>1.05965977</v>
       </c>
       <c r="O20">
-        <v>0.270445735</v>
+        <v>0.2649149425</v>
       </c>
       <c r="P20">
-        <v>0.8113372050000001</v>
+        <v>0.7947448275</v>
       </c>
       <c r="Q20">
-        <v>1.351337205</v>
+        <v>1.3347448275</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1101698307629243</v>
+        <v>0.1107939322828285</v>
       </c>
       <c r="T20">
-        <v>0.9366594698538909</v>
+        <v>0.9457409074130717</v>
       </c>
       <c r="U20">
         <v>0.0613</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.716566035618866</v>
+        <v>3.520957296902083</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09847833514909113</v>
+        <v>0.09876190907258432</v>
       </c>
       <c r="C21">
-        <v>30.93254280050594</v>
+        <v>30.37551672221715</v>
       </c>
       <c r="D21">
-        <v>36.62964280050594</v>
+        <v>36.43351672221715</v>
       </c>
       <c r="E21">
-        <v>6.367100000000001</v>
+        <v>6.728000000000001</v>
       </c>
       <c r="F21">
-        <v>6.857100000000001</v>
+        <v>7.218000000000001</v>
       </c>
       <c r="G21">
         <v>1.16</v>
@@ -3003,45 +3003,45 @@
         <v>1.48</v>
       </c>
       <c r="M21">
-        <v>0.42034023</v>
+        <v>0.4626738000000001</v>
       </c>
       <c r="N21">
-        <v>1.05965977</v>
+        <v>1.0173262</v>
       </c>
       <c r="O21">
-        <v>0.2649149425</v>
+        <v>0.25433155</v>
       </c>
       <c r="P21">
-        <v>0.7947448275</v>
+        <v>0.7629946499999999</v>
       </c>
       <c r="Q21">
-        <v>1.3347448275</v>
+        <v>1.30299465</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1107939322828285</v>
+        <v>0.1114336363407304</v>
       </c>
       <c r="T21">
-        <v>0.9457409074130717</v>
+        <v>0.9550493809112317</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.520957296902083</v>
+        <v>3.198797943605192</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09876190907258432</v>
+        <v>0.09864648299607751</v>
       </c>
       <c r="C22">
-        <v>30.37551672221715</v>
+        <v>30.09419397410169</v>
       </c>
       <c r="D22">
-        <v>36.43351672221715</v>
+        <v>36.51309397410169</v>
       </c>
       <c r="E22">
-        <v>6.728000000000001</v>
+        <v>7.088900000000002</v>
       </c>
       <c r="F22">
-        <v>7.218000000000001</v>
+        <v>7.578900000000002</v>
       </c>
       <c r="G22">
         <v>1.16</v>
@@ -3085,28 +3085,28 @@
         <v>1.48</v>
       </c>
       <c r="M22">
-        <v>0.4626738000000001</v>
+        <v>0.4858074900000001</v>
       </c>
       <c r="N22">
-        <v>1.0173262</v>
+        <v>0.9941925099999999</v>
       </c>
       <c r="O22">
-        <v>0.25433155</v>
+        <v>0.2485481275</v>
       </c>
       <c r="P22">
-        <v>0.7629946499999999</v>
+        <v>0.7456443824999999</v>
       </c>
       <c r="Q22">
-        <v>1.30299465</v>
+        <v>1.2856443825</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1114336363407304</v>
+        <v>0.1120895354380728</v>
       </c>
       <c r="T22">
-        <v>0.9550493809112317</v>
+        <v>0.9645935119663073</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.198797943605192</v>
+        <v>3.046474232004944</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09864648299607751</v>
+        <v>0.09981805691957071</v>
       </c>
       <c r="C23">
-        <v>30.09419397410169</v>
+        <v>28.94137750754296</v>
       </c>
       <c r="D23">
-        <v>36.51309397410169</v>
+        <v>35.72117750754297</v>
       </c>
       <c r="E23">
-        <v>7.088900000000001</v>
+        <v>7.449800000000001</v>
       </c>
       <c r="F23">
-        <v>7.578900000000001</v>
+        <v>7.939800000000001</v>
       </c>
       <c r="G23">
         <v>1.16</v>
@@ -3167,45 +3167,45 @@
         <v>1.48</v>
       </c>
       <c r="M23">
-        <v>0.4858074900000001</v>
+        <v>0.5708716200000001</v>
       </c>
       <c r="N23">
-        <v>0.99419251</v>
+        <v>0.9091283799999998</v>
       </c>
       <c r="O23">
-        <v>0.2485481275</v>
+        <v>0.227282095</v>
       </c>
       <c r="P23">
-        <v>0.7456443825</v>
+        <v>0.6818462849999999</v>
       </c>
       <c r="Q23">
-        <v>1.2856443825</v>
+        <v>1.221846285</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1120895354380728</v>
+        <v>0.1127622524609881</v>
       </c>
       <c r="T23">
-        <v>0.9645935119663073</v>
+        <v>0.9743823643304874</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.046474232004944</v>
+        <v>2.592526845177554</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09981805691957071</v>
+        <v>0.1004338808430639</v>
       </c>
       <c r="C24">
-        <v>28.94137750754296</v>
+        <v>28.17783439771738</v>
       </c>
       <c r="D24">
-        <v>35.72117750754297</v>
+        <v>35.31853439771738</v>
       </c>
       <c r="E24">
-        <v>7.449800000000001</v>
+        <v>7.810700000000001</v>
       </c>
       <c r="F24">
-        <v>7.939800000000001</v>
+        <v>8.300700000000001</v>
       </c>
       <c r="G24">
         <v>1.16</v>
@@ -3249,45 +3249,45 @@
         <v>1.48</v>
       </c>
       <c r="M24">
-        <v>0.5708716200000001</v>
+        <v>0.6291930600000001</v>
       </c>
       <c r="N24">
-        <v>0.9091283799999998</v>
+        <v>0.8508069399999999</v>
       </c>
       <c r="O24">
-        <v>0.227282095</v>
+        <v>0.212701735</v>
       </c>
       <c r="P24">
-        <v>0.6818462849999999</v>
+        <v>0.6381052049999999</v>
       </c>
       <c r="Q24">
-        <v>1.221846285</v>
+        <v>1.178105205</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1127622524609881</v>
+        <v>0.1134524426533297</v>
       </c>
       <c r="T24">
-        <v>0.9743823643304874</v>
+        <v>0.9844254726002307</v>
       </c>
       <c r="U24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.592526845177554</v>
+        <v>2.352219205977891</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1004338808430639</v>
+        <v>0.1004062047665571</v>
       </c>
       <c r="C25">
-        <v>28.17783439771738</v>
+        <v>27.83483489939621</v>
       </c>
       <c r="D25">
-        <v>35.31853439771738</v>
+        <v>35.33643489939622</v>
       </c>
       <c r="E25">
-        <v>7.810700000000001</v>
+        <v>8.171600000000002</v>
       </c>
       <c r="F25">
-        <v>8.300700000000001</v>
+        <v>8.661600000000002</v>
       </c>
       <c r="G25">
         <v>1.16</v>
@@ -3331,28 +3331,28 @@
         <v>1.48</v>
       </c>
       <c r="M25">
-        <v>0.6291930600000001</v>
+        <v>0.6565492800000002</v>
       </c>
       <c r="N25">
-        <v>0.8508069399999999</v>
+        <v>0.8234507199999997</v>
       </c>
       <c r="O25">
-        <v>0.212701735</v>
+        <v>0.2058626799999999</v>
       </c>
       <c r="P25">
-        <v>0.6381052049999999</v>
+        <v>0.6175880399999998</v>
       </c>
       <c r="Q25">
-        <v>1.178105205</v>
+        <v>1.15758804</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1134524426533297</v>
+        <v>0.1141607957454699</v>
       </c>
       <c r="T25">
-        <v>0.9844254726002307</v>
+        <v>0.994732873192862</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.352219205977891</v>
+        <v>2.254210072395479</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1004062047665571</v>
+        <v>0.1003785286900503</v>
       </c>
       <c r="C26">
-        <v>27.83483489939621</v>
+        <v>27.49185355530773</v>
       </c>
       <c r="D26">
-        <v>35.33643489939622</v>
+        <v>35.35435355530773</v>
       </c>
       <c r="E26">
-        <v>8.1716</v>
+        <v>8.532500000000001</v>
       </c>
       <c r="F26">
-        <v>8.6616</v>
+        <v>9.022500000000001</v>
       </c>
       <c r="G26">
         <v>1.16</v>
@@ -3413,28 +3413,28 @@
         <v>1.48</v>
       </c>
       <c r="M26">
-        <v>0.65654928</v>
+        <v>0.6839055000000002</v>
       </c>
       <c r="N26">
-        <v>0.82345072</v>
+        <v>0.7960944999999998</v>
       </c>
       <c r="O26">
-        <v>0.20586268</v>
+        <v>0.199023625</v>
       </c>
       <c r="P26">
-        <v>0.61758804</v>
+        <v>0.5970708749999999</v>
       </c>
       <c r="Q26">
-        <v>1.15758804</v>
+        <v>1.137070875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1141607957454699</v>
+        <v>0.1148880382534004</v>
       </c>
       <c r="T26">
-        <v>0.994732873192862</v>
+        <v>1.005315137801297</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.254210072395479</v>
+        <v>2.16404166949966</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1003785286900503</v>
+        <v>0.1003508526135435</v>
       </c>
       <c r="C27">
-        <v>27.49185355530773</v>
+        <v>27.14889039308324</v>
       </c>
       <c r="D27">
-        <v>35.35435355530773</v>
+        <v>35.37229039308324</v>
       </c>
       <c r="E27">
-        <v>8.532500000000001</v>
+        <v>8.893400000000002</v>
       </c>
       <c r="F27">
-        <v>9.022500000000001</v>
+        <v>9.383400000000002</v>
       </c>
       <c r="G27">
         <v>1.16</v>
@@ -3495,28 +3495,28 @@
         <v>1.48</v>
       </c>
       <c r="M27">
-        <v>0.6839055000000002</v>
+        <v>0.7112617200000002</v>
       </c>
       <c r="N27">
-        <v>0.7960944999999998</v>
+        <v>0.7687382799999998</v>
       </c>
       <c r="O27">
-        <v>0.199023625</v>
+        <v>0.1921845699999999</v>
       </c>
       <c r="P27">
-        <v>0.5970708749999999</v>
+        <v>0.5765537099999998</v>
       </c>
       <c r="Q27">
-        <v>1.137070875</v>
+        <v>1.11655371</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1148880382534004</v>
+        <v>0.115634935964248</v>
       </c>
       <c r="T27">
-        <v>1.005315137801297</v>
+        <v>1.016183409561311</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.16404166949966</v>
+        <v>2.080809297595827</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1003508526135435</v>
+        <v>0.1003231765370367</v>
       </c>
       <c r="C28">
-        <v>27.14889039308324</v>
+        <v>26.80594544041022</v>
       </c>
       <c r="D28">
-        <v>35.37229039308324</v>
+        <v>35.39024544041023</v>
       </c>
       <c r="E28">
-        <v>8.893400000000002</v>
+        <v>9.254300000000001</v>
       </c>
       <c r="F28">
-        <v>9.383400000000002</v>
+        <v>9.744300000000001</v>
       </c>
       <c r="G28">
         <v>1.16</v>
@@ -3577,28 +3577,28 @@
         <v>1.48</v>
       </c>
       <c r="M28">
-        <v>0.7112617200000002</v>
+        <v>0.7386179400000001</v>
       </c>
       <c r="N28">
-        <v>0.7687382799999998</v>
+        <v>0.7413820599999998</v>
       </c>
       <c r="O28">
-        <v>0.1921845699999999</v>
+        <v>0.185345515</v>
       </c>
       <c r="P28">
-        <v>0.5765537099999998</v>
+        <v>0.5560365449999999</v>
       </c>
       <c r="Q28">
-        <v>1.11655371</v>
+        <v>1.096036545</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.115634935964248</v>
+        <v>0.1164022966260777</v>
       </c>
       <c r="T28">
-        <v>1.016183409561311</v>
+        <v>1.027349442191462</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.080809297595827</v>
+        <v>2.003742286573759</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1003231765370367</v>
+        <v>0.1032775004605299</v>
       </c>
       <c r="C29">
-        <v>26.80594544041022</v>
+        <v>24.62599889306256</v>
       </c>
       <c r="D29">
-        <v>35.39024544041023</v>
+        <v>33.57119889306257</v>
       </c>
       <c r="E29">
-        <v>9.254300000000001</v>
+        <v>9.615200000000002</v>
       </c>
       <c r="F29">
-        <v>9.744300000000001</v>
+        <v>10.1052</v>
       </c>
       <c r="G29">
         <v>1.16</v>
@@ -3659,45 +3659,45 @@
         <v>1.48</v>
       </c>
       <c r="M29">
-        <v>0.7386179400000001</v>
+        <v>0.9094680000000002</v>
       </c>
       <c r="N29">
-        <v>0.7413820599999998</v>
+        <v>0.5705319999999998</v>
       </c>
       <c r="O29">
-        <v>0.185345515</v>
+        <v>0.142633</v>
       </c>
       <c r="P29">
-        <v>0.5560365449999999</v>
+        <v>0.4278989999999999</v>
       </c>
       <c r="Q29">
-        <v>1.096036545</v>
+        <v>0.9678989999999998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1164022966260777</v>
+        <v>0.1171909728618471</v>
       </c>
       <c r="T29">
-        <v>1.027349442191462</v>
+        <v>1.038825642394673</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.003742286573759</v>
+        <v>1.627324985595974</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1032775004605299</v>
+        <v>0.1033563243840231</v>
       </c>
       <c r="C30">
-        <v>24.62599889306256</v>
+        <v>24.21912282281414</v>
       </c>
       <c r="D30">
-        <v>33.57119889306257</v>
+        <v>33.52522282281414</v>
       </c>
       <c r="E30">
-        <v>9.615200000000002</v>
+        <v>9.976100000000002</v>
       </c>
       <c r="F30">
-        <v>10.1052</v>
+        <v>10.4661</v>
       </c>
       <c r="G30">
         <v>1.16</v>
@@ -3741,28 +3741,28 @@
         <v>1.48</v>
       </c>
       <c r="M30">
-        <v>0.9094680000000002</v>
+        <v>0.9419490000000001</v>
       </c>
       <c r="N30">
-        <v>0.5705319999999998</v>
+        <v>0.5380509999999998</v>
       </c>
       <c r="O30">
-        <v>0.142633</v>
+        <v>0.13451275</v>
       </c>
       <c r="P30">
-        <v>0.4278989999999999</v>
+        <v>0.4035382499999999</v>
       </c>
       <c r="Q30">
-        <v>0.9678989999999998</v>
+        <v>0.9435382499999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1171909728618471</v>
+        <v>0.11800186532961</v>
       </c>
       <c r="T30">
-        <v>1.038825642394673</v>
+        <v>1.050625115843045</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.627324985595974</v>
+        <v>1.571210330920251</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1033563243840231</v>
+        <v>0.1034351483075163</v>
       </c>
       <c r="C31">
-        <v>24.21912282281415</v>
+        <v>23.81237250965491</v>
       </c>
       <c r="D31">
-        <v>33.52522282281415</v>
+        <v>33.47937250965491</v>
       </c>
       <c r="E31">
-        <v>9.976100000000001</v>
+        <v>10.337</v>
       </c>
       <c r="F31">
-        <v>10.4661</v>
+        <v>10.827</v>
       </c>
       <c r="G31">
         <v>1.16</v>
@@ -3823,28 +3823,28 @@
         <v>1.48</v>
       </c>
       <c r="M31">
-        <v>0.941949</v>
+        <v>0.9744299999999999</v>
       </c>
       <c r="N31">
-        <v>0.5380509999999999</v>
+        <v>0.5055700000000001</v>
       </c>
       <c r="O31">
-        <v>0.13451275</v>
+        <v>0.1263925</v>
       </c>
       <c r="P31">
-        <v>0.40353825</v>
+        <v>0.3791775000000001</v>
       </c>
       <c r="Q31">
-        <v>0.94353825</v>
+        <v>0.9191775000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.11800186532961</v>
+        <v>0.1188359261535947</v>
       </c>
       <c r="T31">
-        <v>1.050625115843045</v>
+        <v>1.062761717104228</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.571210330920251</v>
+        <v>1.51883665322291</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1034351483075163</v>
+        <v>0.1182683335891601</v>
       </c>
       <c r="C32">
-        <v>23.81237250965491</v>
+        <v>16.59874510509976</v>
       </c>
       <c r="D32">
-        <v>33.47937250965491</v>
+        <v>26.62664510509976</v>
       </c>
       <c r="E32">
-        <v>10.337</v>
+        <v>10.6979</v>
       </c>
       <c r="F32">
-        <v>10.827</v>
+        <v>11.1879</v>
       </c>
       <c r="G32">
         <v>1.16</v>
@@ -3905,45 +3905,45 @@
         <v>1.48</v>
       </c>
       <c r="M32">
-        <v>0.9744299999999999</v>
+        <v>1.64238372</v>
       </c>
       <c r="N32">
-        <v>0.5055700000000001</v>
+        <v>-0.1623837200000002</v>
       </c>
       <c r="O32">
-        <v>0.1263925</v>
+        <v>-0.04059593000000006</v>
       </c>
       <c r="P32">
-        <v>0.3791775000000001</v>
+        <v>-0.1217877900000002</v>
       </c>
       <c r="Q32">
-        <v>0.9191775000000001</v>
+        <v>0.4182122099999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1188359261535947</v>
+        <v>0.1203079434759633</v>
       </c>
       <c r="T32">
-        <v>1.062761717104228</v>
+        <v>1.084181362743248</v>
       </c>
       <c r="U32">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.25</v>
+        <v>0.2252823110058592</v>
       </c>
       <c r="W32">
-        <v>0.0675</v>
+        <v>0.1137285567443399</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.51883665322291</v>
+        <v>0.9011292440234367</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1182683335891601</v>
+        <v>0.11927833358916</v>
       </c>
       <c r="C33">
-        <v>16.59874510509976</v>
+        <v>15.87184726270833</v>
       </c>
       <c r="D33">
-        <v>26.62664510509976</v>
+        <v>26.26064726270833</v>
       </c>
       <c r="E33">
-        <v>10.6979</v>
+        <v>11.0588</v>
       </c>
       <c r="F33">
-        <v>11.1879</v>
+        <v>11.5488</v>
       </c>
       <c r="G33">
         <v>1.16</v>
@@ -3987,37 +3987,37 @@
         <v>1.48</v>
       </c>
       <c r="M33">
-        <v>1.64238372</v>
+        <v>1.69536384</v>
       </c>
       <c r="N33">
-        <v>-0.1623837200000002</v>
+        <v>-0.2153638400000004</v>
       </c>
       <c r="O33">
-        <v>-0.04059593000000006</v>
+        <v>-0.0538409600000001</v>
       </c>
       <c r="P33">
-        <v>-0.1217877900000002</v>
+        <v>-0.1615228800000003</v>
       </c>
       <c r="Q33">
-        <v>0.4182122099999999</v>
+        <v>0.3784771199999997</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1203079434759633</v>
+        <v>0.1214036485270804</v>
       </c>
       <c r="T33">
-        <v>1.084181362743248</v>
+        <v>1.100125206313001</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.2252823110058592</v>
+        <v>0.2182422387869261</v>
       </c>
       <c r="W33">
-        <v>0.1137285567443399</v>
+        <v>0.1147620393460793</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9011292440234367</v>
+        <v>0.8729689551477042</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.11927833358916</v>
+        <v>0.1202883335891601</v>
       </c>
       <c r="C34">
-        <v>15.87184726270833</v>
+        <v>15.15487467446082</v>
       </c>
       <c r="D34">
-        <v>26.26064726270833</v>
+        <v>25.90457467446083</v>
       </c>
       <c r="E34">
-        <v>11.0588</v>
+        <v>11.4197</v>
       </c>
       <c r="F34">
-        <v>11.5488</v>
+        <v>11.9097</v>
       </c>
       <c r="G34">
         <v>1.16</v>
@@ -4069,37 +4069,37 @@
         <v>1.48</v>
       </c>
       <c r="M34">
-        <v>1.69536384</v>
+        <v>1.74834396</v>
       </c>
       <c r="N34">
-        <v>-0.2153638400000004</v>
+        <v>-0.2683439600000004</v>
       </c>
       <c r="O34">
-        <v>-0.0538409600000001</v>
+        <v>-0.0670859900000001</v>
       </c>
       <c r="P34">
-        <v>-0.1615228800000003</v>
+        <v>-0.2012579700000003</v>
       </c>
       <c r="Q34">
-        <v>0.3784771199999997</v>
+        <v>0.3387420299999997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1214036485270804</v>
+        <v>0.1225320611916637</v>
       </c>
       <c r="T34">
-        <v>1.100125206313001</v>
+        <v>1.116544985511703</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2182422387869261</v>
+        <v>0.2116288376115647</v>
       </c>
       <c r="W34">
-        <v>0.1147620393460793</v>
+        <v>0.1157328866386223</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8729689551477042</v>
+        <v>0.8465153504462587</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1202883335891601</v>
+        <v>0.12129833358916</v>
       </c>
       <c r="C35">
-        <v>15.15487467446082</v>
+        <v>14.44742900679642</v>
       </c>
       <c r="D35">
-        <v>25.90457467446083</v>
+        <v>25.55802900679642</v>
       </c>
       <c r="E35">
-        <v>11.4197</v>
+        <v>11.7806</v>
       </c>
       <c r="F35">
-        <v>11.9097</v>
+        <v>12.2706</v>
       </c>
       <c r="G35">
         <v>1.16</v>
@@ -4151,37 +4151,37 @@
         <v>1.48</v>
       </c>
       <c r="M35">
-        <v>1.74834396</v>
+        <v>1.80132408</v>
       </c>
       <c r="N35">
-        <v>-0.2683439600000004</v>
+        <v>-0.3213240800000003</v>
       </c>
       <c r="O35">
-        <v>-0.0670859900000001</v>
+        <v>-0.08033102000000009</v>
       </c>
       <c r="P35">
-        <v>-0.2012579700000003</v>
+        <v>-0.2409930600000003</v>
       </c>
       <c r="Q35">
-        <v>0.3387420299999997</v>
+        <v>0.2990069399999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1225320611916637</v>
+        <v>0.1236946681794162</v>
       </c>
       <c r="T35">
-        <v>1.116544985511703</v>
+        <v>1.133462333777032</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2116288376115647</v>
+        <v>0.205404460034754</v>
       </c>
       <c r="W35">
-        <v>0.1157328866386223</v>
+        <v>0.1166466252668981</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8465153504462587</v>
+        <v>0.8216178401390158</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.12129833358916</v>
+        <v>0.142246367845298</v>
       </c>
       <c r="C36">
-        <v>14.44742900679642</v>
+        <v>8.535356068770209</v>
       </c>
       <c r="D36">
-        <v>25.55802900679642</v>
+        <v>20.00685606877021</v>
       </c>
       <c r="E36">
-        <v>11.7806</v>
+        <v>12.1415</v>
       </c>
       <c r="F36">
-        <v>12.2706</v>
+        <v>12.6315</v>
       </c>
       <c r="G36">
         <v>1.16</v>
@@ -4233,45 +4233,45 @@
         <v>1.48</v>
       </c>
       <c r="M36">
-        <v>1.80132408</v>
+        <v>2.536405200000001</v>
       </c>
       <c r="N36">
-        <v>-0.3213240800000003</v>
+        <v>-1.056405200000001</v>
       </c>
       <c r="O36">
-        <v>-0.08033102000000009</v>
+        <v>-0.2641013000000002</v>
       </c>
       <c r="P36">
-        <v>-0.2409930600000003</v>
+        <v>-0.7923039000000006</v>
       </c>
       <c r="Q36">
-        <v>0.2990069399999998</v>
+        <v>-0.2523039000000006</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1236946681794162</v>
+        <v>0.1264900234685426</v>
       </c>
       <c r="T36">
-        <v>1.133462333777032</v>
+        <v>1.174138159270649</v>
       </c>
       <c r="U36">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.205404460034754</v>
+        <v>0.1458757457207547</v>
       </c>
       <c r="W36">
-        <v>0.1166466252668981</v>
+        <v>0.1715081502592725</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8216178401390158</v>
+        <v>0.5835029828830187</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.142246367845298</v>
+        <v>0.143796367845298</v>
       </c>
       <c r="C37">
-        <v>8.535356068770209</v>
+        <v>7.858009371933967</v>
       </c>
       <c r="D37">
-        <v>20.00685606877021</v>
+        <v>19.69040937193397</v>
       </c>
       <c r="E37">
-        <v>12.1415</v>
+        <v>12.5024</v>
       </c>
       <c r="F37">
-        <v>12.6315</v>
+        <v>12.9924</v>
       </c>
       <c r="G37">
         <v>1.16</v>
@@ -4315,37 +4315,37 @@
         <v>1.48</v>
       </c>
       <c r="M37">
-        <v>2.536405200000001</v>
+        <v>2.608873920000001</v>
       </c>
       <c r="N37">
-        <v>-1.056405200000001</v>
+        <v>-1.128873920000001</v>
       </c>
       <c r="O37">
-        <v>-0.2641013000000002</v>
+        <v>-0.2822184800000002</v>
       </c>
       <c r="P37">
-        <v>-0.7923039000000006</v>
+        <v>-0.8466554400000005</v>
       </c>
       <c r="Q37">
-        <v>-0.2523039000000006</v>
+        <v>-0.3066554400000004</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1264900234685426</v>
+        <v>0.1277508050852385</v>
       </c>
       <c r="T37">
-        <v>1.174138159270649</v>
+        <v>1.192484068009253</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1458757457207547</v>
+        <v>0.1418236416729559</v>
       </c>
       <c r="W37">
-        <v>0.1715081502592725</v>
+        <v>0.1723218127520705</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5835029828830187</v>
+        <v>0.5672945666918238</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.143796367845298</v>
+        <v>0.145346367845298</v>
       </c>
       <c r="C38">
-        <v>7.858009371933971</v>
+        <v>7.190517226111751</v>
       </c>
       <c r="D38">
-        <v>19.69040937193397</v>
+        <v>19.38381722611175</v>
       </c>
       <c r="E38">
-        <v>12.5024</v>
+        <v>12.8633</v>
       </c>
       <c r="F38">
-        <v>12.9924</v>
+        <v>13.3533</v>
       </c>
       <c r="G38">
         <v>1.16</v>
@@ -4397,37 +4397,37 @@
         <v>1.48</v>
       </c>
       <c r="M38">
-        <v>2.60887392</v>
+        <v>2.68134264</v>
       </c>
       <c r="N38">
-        <v>-1.12887392</v>
+        <v>-1.20134264</v>
       </c>
       <c r="O38">
-        <v>-0.28221848</v>
+        <v>-0.3003356600000001</v>
       </c>
       <c r="P38">
-        <v>-0.8466554400000001</v>
+        <v>-0.9010069800000003</v>
       </c>
       <c r="Q38">
-        <v>-0.3066554400000001</v>
+        <v>-0.3610069800000003</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1277508050852385</v>
+        <v>0.129051611515163</v>
       </c>
       <c r="T38">
-        <v>1.192484068009253</v>
+        <v>1.211412386549082</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.141823641672956</v>
+        <v>0.1379905702763896</v>
       </c>
       <c r="W38">
-        <v>0.1723218127520705</v>
+        <v>0.173091493488501</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5672945666918239</v>
+        <v>0.5519622811055582</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.145346367845298</v>
+        <v>0.146896367845298</v>
       </c>
       <c r="C39">
-        <v>7.190517226111751</v>
+        <v>6.53242636415666</v>
       </c>
       <c r="D39">
-        <v>19.38381722611175</v>
+        <v>19.08662636415666</v>
       </c>
       <c r="E39">
-        <v>12.8633</v>
+        <v>13.2242</v>
       </c>
       <c r="F39">
-        <v>13.3533</v>
+        <v>13.7142</v>
       </c>
       <c r="G39">
         <v>1.16</v>
@@ -4479,37 +4479,37 @@
         <v>1.48</v>
       </c>
       <c r="M39">
-        <v>2.68134264</v>
+        <v>2.75381136</v>
       </c>
       <c r="N39">
-        <v>-1.20134264</v>
+        <v>-1.27381136</v>
       </c>
       <c r="O39">
-        <v>-0.3003356600000001</v>
+        <v>-0.3184528400000001</v>
       </c>
       <c r="P39">
-        <v>-0.9010069800000003</v>
+        <v>-0.9553585200000002</v>
       </c>
       <c r="Q39">
-        <v>-0.3610069800000003</v>
+        <v>-0.4153585200000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.129051611515163</v>
+        <v>0.1303943794428269</v>
       </c>
       <c r="T39">
-        <v>1.211412386549082</v>
+        <v>1.230951296009551</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1379905702763896</v>
+        <v>0.1343592394796425</v>
       </c>
       <c r="W39">
-        <v>0.173091493488501</v>
+        <v>0.1738206647124878</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5519622811055582</v>
+        <v>0.5374369579185699</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.146896367845298</v>
+        <v>0.148446367845298</v>
       </c>
       <c r="C40">
-        <v>6.53242636415666</v>
+        <v>5.883310896961262</v>
       </c>
       <c r="D40">
-        <v>19.08662636415666</v>
+        <v>18.79841089696126</v>
       </c>
       <c r="E40">
-        <v>13.2242</v>
+        <v>13.5851</v>
       </c>
       <c r="F40">
-        <v>13.7142</v>
+        <v>14.0751</v>
       </c>
       <c r="G40">
         <v>1.16</v>
@@ -4561,37 +4561,37 @@
         <v>1.48</v>
       </c>
       <c r="M40">
-        <v>2.75381136</v>
+        <v>2.826280080000001</v>
       </c>
       <c r="N40">
-        <v>-1.27381136</v>
+        <v>-1.346280080000001</v>
       </c>
       <c r="O40">
-        <v>-0.3184528400000001</v>
+        <v>-0.3365700200000001</v>
       </c>
       <c r="P40">
-        <v>-0.9553585200000002</v>
+        <v>-1.00971006</v>
       </c>
       <c r="Q40">
-        <v>-0.4153585200000002</v>
+        <v>-0.4697100600000004</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1303943794428269</v>
+        <v>0.131781172548447</v>
       </c>
       <c r="T40">
-        <v>1.230951296009551</v>
+        <v>1.251130825452331</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1343592394796425</v>
+        <v>0.1309141307750362</v>
       </c>
       <c r="W40">
-        <v>0.1738206647124878</v>
+        <v>0.1745124425403727</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5374369579185699</v>
+        <v>0.5236565231001451</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.148446367845298</v>
+        <v>0.149996367845298</v>
       </c>
       <c r="C41">
-        <v>5.883310896961262</v>
+        <v>5.242770277112109</v>
       </c>
       <c r="D41">
-        <v>18.79841089696126</v>
+        <v>18.51877027711211</v>
       </c>
       <c r="E41">
-        <v>13.5851</v>
+        <v>13.946</v>
       </c>
       <c r="F41">
-        <v>14.0751</v>
+        <v>14.436</v>
       </c>
       <c r="G41">
         <v>1.16</v>
@@ -4643,37 +4643,37 @@
         <v>1.48</v>
       </c>
       <c r="M41">
-        <v>2.826280080000001</v>
+        <v>2.8987488</v>
       </c>
       <c r="N41">
-        <v>-1.346280080000001</v>
+        <v>-1.4187488</v>
       </c>
       <c r="O41">
-        <v>-0.3365700200000001</v>
+        <v>-0.3546872000000001</v>
       </c>
       <c r="P41">
-        <v>-1.00971006</v>
+        <v>-1.0640616</v>
       </c>
       <c r="Q41">
-        <v>-0.4697100600000004</v>
+        <v>-0.5240616000000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.131781172548447</v>
+        <v>0.1332141920909211</v>
       </c>
       <c r="T41">
-        <v>1.251130825452331</v>
+        <v>1.271983005876536</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1309141307750362</v>
+        <v>0.1276412775056603</v>
       </c>
       <c r="W41">
-        <v>0.1745124425403727</v>
+        <v>0.1751696314768634</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5236565231001451</v>
+        <v>0.5105651100226414</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.149996367845298</v>
+        <v>0.1663152272057131</v>
       </c>
       <c r="C42">
-        <v>5.242770277112109</v>
+        <v>2.374260121225506</v>
       </c>
       <c r="D42">
-        <v>18.51877027711211</v>
+        <v>16.01116012122551</v>
       </c>
       <c r="E42">
-        <v>13.946</v>
+        <v>14.3069</v>
       </c>
       <c r="F42">
-        <v>14.436</v>
+        <v>14.7969</v>
       </c>
       <c r="G42">
         <v>1.16</v>
@@ -4725,45 +4725,45 @@
         <v>1.48</v>
       </c>
       <c r="M42">
-        <v>2.8987488</v>
+        <v>3.489109020000001</v>
       </c>
       <c r="N42">
-        <v>-1.4187488</v>
+        <v>-2.009109020000001</v>
       </c>
       <c r="O42">
-        <v>-0.3546872000000001</v>
+        <v>-0.5022772550000002</v>
       </c>
       <c r="P42">
-        <v>-1.0640616</v>
+        <v>-1.506831765000001</v>
       </c>
       <c r="Q42">
-        <v>-0.5240616000000002</v>
+        <v>-0.9668317650000007</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1332141920909211</v>
+        <v>0.135405719686386</v>
       </c>
       <c r="T42">
-        <v>1.271983005876536</v>
+        <v>1.30387240268571</v>
       </c>
       <c r="U42">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.1276412775056603</v>
+        <v>0.1060442645612718</v>
       </c>
       <c r="W42">
-        <v>0.1751696314768634</v>
+        <v>0.2107947624164521</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.5105651100226414</v>
+        <v>0.4241770582450873</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1663152272057131</v>
+        <v>0.1682152272057131</v>
       </c>
       <c r="C43">
-        <v>2.374260121225506</v>
+        <v>1.764851786725524</v>
       </c>
       <c r="D43">
-        <v>16.01116012122551</v>
+        <v>15.76265178672553</v>
       </c>
       <c r="E43">
-        <v>14.3069</v>
+        <v>14.6678</v>
       </c>
       <c r="F43">
-        <v>14.7969</v>
+        <v>15.1578</v>
       </c>
       <c r="G43">
         <v>1.16</v>
@@ -4807,37 +4807,37 @@
         <v>1.48</v>
       </c>
       <c r="M43">
-        <v>3.489109020000001</v>
+        <v>3.574209240000001</v>
       </c>
       <c r="N43">
-        <v>-2.009109020000001</v>
+        <v>-2.094209240000001</v>
       </c>
       <c r="O43">
-        <v>-0.5022772550000002</v>
+        <v>-0.5235523100000002</v>
       </c>
       <c r="P43">
-        <v>-1.506831765000001</v>
+        <v>-1.570656930000001</v>
       </c>
       <c r="Q43">
-        <v>-0.9668317650000007</v>
+        <v>-1.030656930000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.135405719686386</v>
+        <v>0.1369506458878753</v>
       </c>
       <c r="T43">
-        <v>1.30387240268571</v>
+        <v>1.326352961352705</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1060442645612718</v>
+        <v>0.1035194011193368</v>
       </c>
       <c r="W43">
-        <v>0.2107947624164521</v>
+        <v>0.2113901252160604</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4241770582450873</v>
+        <v>0.4140776044773472</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1682152272057131</v>
+        <v>0.1701152272057131</v>
       </c>
       <c r="C44">
-        <v>1.764851786725526</v>
+        <v>1.163039719330763</v>
       </c>
       <c r="D44">
-        <v>15.76265178672553</v>
+        <v>15.52173971933076</v>
       </c>
       <c r="E44">
-        <v>14.6678</v>
+        <v>15.0287</v>
       </c>
       <c r="F44">
-        <v>15.1578</v>
+        <v>15.5187</v>
       </c>
       <c r="G44">
         <v>1.16</v>
@@ -4889,37 +4889,37 @@
         <v>1.48</v>
       </c>
       <c r="M44">
-        <v>3.574209240000001</v>
+        <v>3.65930946</v>
       </c>
       <c r="N44">
-        <v>-2.094209240000001</v>
+        <v>-2.17930946</v>
       </c>
       <c r="O44">
-        <v>-0.5235523100000001</v>
+        <v>-0.5448273650000001</v>
       </c>
       <c r="P44">
-        <v>-1.57065693</v>
+        <v>-1.634482095</v>
       </c>
       <c r="Q44">
-        <v>-1.03065693</v>
+        <v>-1.094482095</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1369506458878753</v>
+        <v>0.1385497800262591</v>
       </c>
       <c r="T44">
-        <v>1.326352961352705</v>
+        <v>1.349622311551875</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1035194011193368</v>
+        <v>0.101111973186329</v>
       </c>
       <c r="W44">
-        <v>0.2113901252160604</v>
+        <v>0.2119577967226636</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4140776044773472</v>
+        <v>0.4044478927453159</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1701152272057131</v>
+        <v>0.1720152272057131</v>
       </c>
       <c r="C45">
-        <v>1.163039719330763</v>
+        <v>0.5684808643761112</v>
       </c>
       <c r="D45">
-        <v>15.52173971933076</v>
+        <v>15.28808086437611</v>
       </c>
       <c r="E45">
-        <v>15.0287</v>
+        <v>15.3896</v>
       </c>
       <c r="F45">
-        <v>15.5187</v>
+        <v>15.8796</v>
       </c>
       <c r="G45">
         <v>1.16</v>
@@ -4971,37 +4971,37 @@
         <v>1.48</v>
       </c>
       <c r="M45">
-        <v>3.65930946</v>
+        <v>3.74440968</v>
       </c>
       <c r="N45">
-        <v>-2.17930946</v>
+        <v>-2.26440968</v>
       </c>
       <c r="O45">
-        <v>-0.5448273650000001</v>
+        <v>-0.5661024200000001</v>
       </c>
       <c r="P45">
-        <v>-1.634482095</v>
+        <v>-1.69830726</v>
       </c>
       <c r="Q45">
-        <v>-1.094482095</v>
+        <v>-1.15830726</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1385497800262591</v>
+        <v>0.1402060260981566</v>
       </c>
       <c r="T45">
-        <v>1.349622311551875</v>
+        <v>1.373722709972445</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.101111973186329</v>
+        <v>0.09881397379573059</v>
       </c>
       <c r="W45">
-        <v>0.2119577967226636</v>
+        <v>0.2124996649789667</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4044478927453159</v>
+        <v>0.3952558951829224</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1720152272057131</v>
+        <v>0.1739152272057131</v>
       </c>
       <c r="C46">
-        <v>0.5684808643761112</v>
+        <v>-0.0191474822526132</v>
       </c>
       <c r="D46">
-        <v>15.28808086437611</v>
+        <v>15.06135251774739</v>
       </c>
       <c r="E46">
-        <v>15.3896</v>
+        <v>15.7505</v>
       </c>
       <c r="F46">
-        <v>15.8796</v>
+        <v>16.2405</v>
       </c>
       <c r="G46">
         <v>1.16</v>
@@ -5053,37 +5053,37 @@
         <v>1.48</v>
       </c>
       <c r="M46">
-        <v>3.74440968</v>
+        <v>3.8295099</v>
       </c>
       <c r="N46">
-        <v>-2.26440968</v>
+        <v>-2.3495099</v>
       </c>
       <c r="O46">
-        <v>-0.5661024200000001</v>
+        <v>-0.587377475</v>
       </c>
       <c r="P46">
-        <v>-1.69830726</v>
+        <v>-1.762132425</v>
       </c>
       <c r="Q46">
-        <v>-1.15830726</v>
+        <v>-1.222132425</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1402060260981566</v>
+        <v>0.1419224992999413</v>
       </c>
       <c r="T46">
-        <v>1.373722709972445</v>
+        <v>1.398699486517398</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09881397379573059</v>
+        <v>0.09661810771138103</v>
       </c>
       <c r="W46">
-        <v>0.2124996649789667</v>
+        <v>0.2130174502016564</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3952558951829224</v>
+        <v>0.3864724308455241</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1739152272057131</v>
+        <v>0.1758152272057131</v>
       </c>
       <c r="C47">
-        <v>-0.0191474822526132</v>
+        <v>-0.6001491611001448</v>
       </c>
       <c r="D47">
-        <v>15.06135251774739</v>
+        <v>14.84125083889986</v>
       </c>
       <c r="E47">
-        <v>15.7505</v>
+        <v>16.1114</v>
       </c>
       <c r="F47">
-        <v>16.2405</v>
+        <v>16.6014</v>
       </c>
       <c r="G47">
         <v>1.16</v>
@@ -5135,37 +5135,37 @@
         <v>1.48</v>
       </c>
       <c r="M47">
-        <v>3.8295099</v>
+        <v>3.914610120000001</v>
       </c>
       <c r="N47">
-        <v>-2.3495099</v>
+        <v>-2.434610120000001</v>
       </c>
       <c r="O47">
-        <v>-0.587377475</v>
+        <v>-0.6086525300000002</v>
       </c>
       <c r="P47">
-        <v>-1.762132425</v>
+        <v>-1.825957590000001</v>
       </c>
       <c r="Q47">
-        <v>-1.222132425</v>
+        <v>-1.285957590000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1419224992999413</v>
+        <v>0.1437025455832735</v>
       </c>
       <c r="T47">
-        <v>1.398699486517398</v>
+        <v>1.424601328860313</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09661810771138103</v>
+        <v>0.09451771406548143</v>
       </c>
       <c r="W47">
-        <v>0.2130174502016564</v>
+        <v>0.2135127230233595</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3864724308455241</v>
+        <v>0.3780708562619257</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1758152272057131</v>
+        <v>0.1777152272057131</v>
       </c>
       <c r="C48">
-        <v>-0.6001491611001448</v>
+        <v>-1.174810507619574</v>
       </c>
       <c r="D48">
-        <v>14.84125083889986</v>
+        <v>14.62748949238043</v>
       </c>
       <c r="E48">
-        <v>16.1114</v>
+        <v>16.4723</v>
       </c>
       <c r="F48">
-        <v>16.6014</v>
+        <v>16.9623</v>
       </c>
       <c r="G48">
         <v>1.16</v>
@@ -5217,37 +5217,37 @@
         <v>1.48</v>
       </c>
       <c r="M48">
-        <v>3.914610120000001</v>
+        <v>3.999710340000001</v>
       </c>
       <c r="N48">
-        <v>-2.434610120000001</v>
+        <v>-2.519710340000001</v>
       </c>
       <c r="O48">
-        <v>-0.6086525300000002</v>
+        <v>-0.6299275850000002</v>
       </c>
       <c r="P48">
-        <v>-1.825957590000001</v>
+        <v>-1.889782755000001</v>
       </c>
       <c r="Q48">
-        <v>-1.285957590000001</v>
+        <v>-1.349782755000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1437025455832735</v>
+        <v>0.1455497634244674</v>
       </c>
       <c r="T48">
-        <v>1.424601328860313</v>
+        <v>1.451480599216168</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09451771406548143</v>
+        <v>0.09250669887259884</v>
       </c>
       <c r="W48">
-        <v>0.2135127230233595</v>
+        <v>0.2139869204058412</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3780708562619257</v>
+        <v>0.3700267954903953</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1777152272057131</v>
+        <v>0.1796152272057131</v>
       </c>
       <c r="C49">
-        <v>-1.174810507619574</v>
+        <v>-1.743401594918618</v>
       </c>
       <c r="D49">
-        <v>14.62748949238043</v>
+        <v>14.41979840508139</v>
       </c>
       <c r="E49">
-        <v>16.4723</v>
+        <v>16.83320000000001</v>
       </c>
       <c r="F49">
-        <v>16.9623</v>
+        <v>17.3232</v>
       </c>
       <c r="G49">
         <v>1.16</v>
@@ -5299,37 +5299,37 @@
         <v>1.48</v>
       </c>
       <c r="M49">
-        <v>3.999710340000001</v>
+        <v>4.084810560000001</v>
       </c>
       <c r="N49">
-        <v>-2.519710340000001</v>
+        <v>-2.604810560000001</v>
       </c>
       <c r="O49">
-        <v>-0.6299275850000002</v>
+        <v>-0.6512026400000003</v>
       </c>
       <c r="P49">
-        <v>-1.889782755000001</v>
+        <v>-1.953607920000001</v>
       </c>
       <c r="Q49">
-        <v>-1.349782755000001</v>
+        <v>-1.413607920000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1455497634244674</v>
+        <v>0.1474680281057071</v>
       </c>
       <c r="T49">
-        <v>1.451480599216168</v>
+        <v>1.479393687662633</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.09250669887259884</v>
+        <v>0.09057947597941969</v>
       </c>
       <c r="W49">
-        <v>0.2139869204058412</v>
+        <v>0.2144413595640528</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3700267954903953</v>
+        <v>0.3623179039176788</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.179615227205713</v>
+        <v>0.1815152272057131</v>
       </c>
       <c r="C50">
-        <v>-1.743401594918611</v>
+        <v>-2.306177372115862</v>
       </c>
       <c r="D50">
-        <v>14.41979840508139</v>
+        <v>14.21792262788414</v>
       </c>
       <c r="E50">
-        <v>16.8332</v>
+        <v>17.1941</v>
       </c>
       <c r="F50">
-        <v>17.3232</v>
+        <v>17.6841</v>
       </c>
       <c r="G50">
         <v>1.16</v>
@@ -5381,37 +5381,37 @@
         <v>1.48</v>
       </c>
       <c r="M50">
-        <v>4.08481056</v>
+        <v>4.16991078</v>
       </c>
       <c r="N50">
-        <v>-2.60481056</v>
+        <v>-2.68991078</v>
       </c>
       <c r="O50">
-        <v>-0.6512026400000001</v>
+        <v>-0.6724776950000001</v>
       </c>
       <c r="P50">
-        <v>-1.95360792</v>
+        <v>-2.017433085</v>
       </c>
       <c r="Q50">
-        <v>-1.41360792</v>
+        <v>-1.477433085</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1474680281057071</v>
+        <v>0.1494615188528778</v>
       </c>
       <c r="T50">
-        <v>1.479393687662632</v>
+        <v>1.508401407028567</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0905794759794197</v>
+        <v>0.08873091524514584</v>
       </c>
       <c r="W50">
-        <v>0.2144413595640528</v>
+        <v>0.2148772501851946</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3623179039176788</v>
+        <v>0.3549236609805834</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1815152272057131</v>
+        <v>0.1834152272057131</v>
       </c>
       <c r="C51">
-        <v>-2.306177372115862</v>
+        <v>-2.863378708396027</v>
       </c>
       <c r="D51">
-        <v>14.21792262788414</v>
+        <v>14.02162129160397</v>
       </c>
       <c r="E51">
-        <v>17.1941</v>
+        <v>17.555</v>
       </c>
       <c r="F51">
-        <v>17.6841</v>
+        <v>18.045</v>
       </c>
       <c r="G51">
         <v>1.16</v>
@@ -5463,37 +5463,37 @@
         <v>1.48</v>
       </c>
       <c r="M51">
-        <v>4.16991078</v>
+        <v>4.255011000000001</v>
       </c>
       <c r="N51">
-        <v>-2.68991078</v>
+        <v>-2.775011000000001</v>
       </c>
       <c r="O51">
-        <v>-0.6724776950000001</v>
+        <v>-0.6937527500000001</v>
       </c>
       <c r="P51">
-        <v>-2.017433085</v>
+        <v>-2.08125825</v>
       </c>
       <c r="Q51">
-        <v>-1.477433085</v>
+        <v>-1.54125825</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1494615188528778</v>
+        <v>0.1515347492299354</v>
       </c>
       <c r="T51">
-        <v>1.508401407028567</v>
+        <v>1.538569435169138</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08873091524514584</v>
+        <v>0.08695629694024291</v>
       </c>
       <c r="W51">
-        <v>0.2148772501851946</v>
+        <v>0.2152957051814907</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3549236609805834</v>
+        <v>0.3478251877609717</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1834152272057131</v>
+        <v>0.1853152272057131</v>
       </c>
       <c r="C52">
-        <v>-2.863378708396027</v>
+        <v>-3.415233351753816</v>
       </c>
       <c r="D52">
-        <v>14.02162129160397</v>
+        <v>13.83066664824619</v>
       </c>
       <c r="E52">
-        <v>17.555</v>
+        <v>17.9159</v>
       </c>
       <c r="F52">
-        <v>18.045</v>
+        <v>18.4059</v>
       </c>
       <c r="G52">
         <v>1.16</v>
@@ -5545,37 +5545,37 @@
         <v>1.48</v>
       </c>
       <c r="M52">
-        <v>4.255011000000001</v>
+        <v>4.340111220000001</v>
       </c>
       <c r="N52">
-        <v>-2.775011000000001</v>
+        <v>-2.860111220000001</v>
       </c>
       <c r="O52">
-        <v>-0.6937527500000001</v>
+        <v>-0.7150278050000002</v>
       </c>
       <c r="P52">
-        <v>-2.08125825</v>
+        <v>-2.145083415000001</v>
       </c>
       <c r="Q52">
-        <v>-1.54125825</v>
+        <v>-1.605083415000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1515347492299354</v>
+        <v>0.1536926012550361</v>
       </c>
       <c r="T52">
-        <v>1.538569435169138</v>
+        <v>1.56996881139708</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08695629694024291</v>
+        <v>0.08525127151004207</v>
       </c>
       <c r="W52">
-        <v>0.2152957051814907</v>
+        <v>0.2156977501779321</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3478251877609717</v>
+        <v>0.3410050860401683</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1853152272057131</v>
+        <v>0.1872152272057131</v>
       </c>
       <c r="C53">
-        <v>-3.415233351753816</v>
+        <v>-3.961956810449971</v>
       </c>
       <c r="D53">
-        <v>13.83066664824619</v>
+        <v>13.64484318955003</v>
       </c>
       <c r="E53">
-        <v>17.9159</v>
+        <v>18.27680000000001</v>
       </c>
       <c r="F53">
-        <v>18.4059</v>
+        <v>18.7668</v>
       </c>
       <c r="G53">
         <v>1.16</v>
@@ -5627,37 +5627,37 @@
         <v>1.48</v>
       </c>
       <c r="M53">
-        <v>4.340111220000001</v>
+        <v>4.425211440000001</v>
       </c>
       <c r="N53">
-        <v>-2.860111220000001</v>
+        <v>-2.945211440000001</v>
       </c>
       <c r="O53">
-        <v>-0.7150278050000002</v>
+        <v>-0.7363028600000002</v>
       </c>
       <c r="P53">
-        <v>-2.145083415000001</v>
+        <v>-2.208908580000001</v>
       </c>
       <c r="Q53">
-        <v>-1.605083415000001</v>
+        <v>-1.668908580000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1536926012550361</v>
+        <v>0.1559403637811827</v>
       </c>
       <c r="T53">
-        <v>1.56996881139708</v>
+        <v>1.602676494967852</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08525127151004207</v>
+        <v>0.08361182398100279</v>
       </c>
       <c r="W53">
-        <v>0.2156977501779321</v>
+        <v>0.2160843319052796</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3410050860401683</v>
+        <v>0.3344472959240112</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1872152272057131</v>
+        <v>0.1891152272057131</v>
       </c>
       <c r="C54">
-        <v>-3.961956810449971</v>
+        <v>-4.503753164351936</v>
       </c>
       <c r="D54">
-        <v>13.64484318955003</v>
+        <v>13.46394683564807</v>
       </c>
       <c r="E54">
-        <v>18.27680000000001</v>
+        <v>18.63770000000001</v>
       </c>
       <c r="F54">
-        <v>18.7668</v>
+        <v>19.1277</v>
       </c>
       <c r="G54">
         <v>1.16</v>
@@ -5709,37 +5709,37 @@
         <v>1.48</v>
       </c>
       <c r="M54">
-        <v>4.425211440000001</v>
+        <v>4.510311660000001</v>
       </c>
       <c r="N54">
-        <v>-2.945211440000001</v>
+        <v>-3.030311660000001</v>
       </c>
       <c r="O54">
-        <v>-0.7363028600000002</v>
+        <v>-0.7575779150000003</v>
       </c>
       <c r="P54">
-        <v>-2.208908580000001</v>
+        <v>-2.272733745000001</v>
       </c>
       <c r="Q54">
-        <v>-1.668908580000001</v>
+        <v>-1.732733745000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1559403637811827</v>
+        <v>0.1582837757765271</v>
       </c>
       <c r="T54">
-        <v>1.602676494967852</v>
+        <v>1.636775994860785</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08361182398100279</v>
+        <v>0.08203424239645557</v>
       </c>
       <c r="W54">
-        <v>0.2160843319052796</v>
+        <v>0.2164563256429158</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3344472959240112</v>
+        <v>0.3281369695858223</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1891152272057131</v>
+        <v>0.1910152272057131</v>
       </c>
       <c r="C55">
-        <v>-4.503753164351936</v>
+        <v>-5.040815812580909</v>
       </c>
       <c r="D55">
-        <v>13.46394683564807</v>
+        <v>13.28778418741909</v>
       </c>
       <c r="E55">
-        <v>18.63770000000001</v>
+        <v>18.9986</v>
       </c>
       <c r="F55">
-        <v>19.1277</v>
+        <v>19.4886</v>
       </c>
       <c r="G55">
         <v>1.16</v>
@@ -5791,37 +5791,37 @@
         <v>1.48</v>
       </c>
       <c r="M55">
-        <v>4.510311660000001</v>
+        <v>4.59541188</v>
       </c>
       <c r="N55">
-        <v>-3.030311660000001</v>
+        <v>-3.11541188</v>
       </c>
       <c r="O55">
-        <v>-0.7575779150000003</v>
+        <v>-0.7788529700000001</v>
       </c>
       <c r="P55">
-        <v>-2.272733745000001</v>
+        <v>-2.33655891</v>
       </c>
       <c r="Q55">
-        <v>-1.732733745000001</v>
+        <v>-1.79655891</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1582837757765271</v>
+        <v>0.1607290752499298</v>
       </c>
       <c r="T55">
-        <v>1.636775994860785</v>
+        <v>1.672358081705585</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.08203424239645557</v>
+        <v>0.08051508975948418</v>
       </c>
       <c r="W55">
-        <v>0.2164563256429158</v>
+        <v>0.2168145418347136</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3281369695858223</v>
+        <v>0.3220603590379367</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1910152272057131</v>
+        <v>0.1929152272057131</v>
       </c>
       <c r="C56">
-        <v>-5.040815812580909</v>
+        <v>-5.573328163223538</v>
       </c>
       <c r="D56">
-        <v>13.28778418741909</v>
+        <v>13.11617183677646</v>
       </c>
       <c r="E56">
-        <v>18.9986</v>
+        <v>19.3595</v>
       </c>
       <c r="F56">
-        <v>19.4886</v>
+        <v>19.8495</v>
       </c>
       <c r="G56">
         <v>1.16</v>
@@ -5873,37 +5873,37 @@
         <v>1.48</v>
       </c>
       <c r="M56">
-        <v>4.59541188</v>
+        <v>4.680512100000001</v>
       </c>
       <c r="N56">
-        <v>-3.11541188</v>
+        <v>-3.200512100000001</v>
       </c>
       <c r="O56">
-        <v>-0.7788529700000001</v>
+        <v>-0.8001280250000001</v>
       </c>
       <c r="P56">
-        <v>-2.33655891</v>
+        <v>-2.400384075</v>
       </c>
       <c r="Q56">
-        <v>-1.79655891</v>
+        <v>-1.860384075</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1607290752499298</v>
+        <v>0.1632830546999283</v>
       </c>
       <c r="T56">
-        <v>1.672358081705585</v>
+        <v>1.709521594632376</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.08051508975948418</v>
+        <v>0.07905117903658447</v>
       </c>
       <c r="W56">
-        <v>0.2168145418347136</v>
+        <v>0.2171597319831734</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3220603590379367</v>
+        <v>0.3162047161463378</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1929152272057131</v>
+        <v>0.1948152272057131</v>
       </c>
       <c r="C57">
-        <v>-5.573328163223538</v>
+        <v>-6.101464270279044</v>
       </c>
       <c r="D57">
-        <v>13.11617183677646</v>
+        <v>12.94893572972096</v>
       </c>
       <c r="E57">
-        <v>19.3595</v>
+        <v>19.72040000000001</v>
       </c>
       <c r="F57">
-        <v>19.8495</v>
+        <v>20.2104</v>
       </c>
       <c r="G57">
         <v>1.16</v>
@@ -5955,37 +5955,37 @@
         <v>1.48</v>
       </c>
       <c r="M57">
-        <v>4.680512100000001</v>
+        <v>4.765612320000001</v>
       </c>
       <c r="N57">
-        <v>-3.200512100000001</v>
+        <v>-3.285612320000001</v>
       </c>
       <c r="O57">
-        <v>-0.8001280250000001</v>
+        <v>-0.8214030800000002</v>
       </c>
       <c r="P57">
-        <v>-2.400384075</v>
+        <v>-2.464209240000001</v>
       </c>
       <c r="Q57">
-        <v>-1.860384075</v>
+        <v>-1.924209240000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1632830546999283</v>
+        <v>0.1659531241249266</v>
       </c>
       <c r="T57">
-        <v>1.709521594632376</v>
+        <v>1.748374358146748</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07905117903658447</v>
+        <v>0.07763955083950261</v>
       </c>
       <c r="W57">
-        <v>0.2171597319831734</v>
+        <v>0.2174925939120453</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3162047161463378</v>
+        <v>0.3105582033580104</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1948152272057131</v>
+        <v>0.1967152272057131</v>
       </c>
       <c r="C58">
-        <v>-6.101464270279044</v>
+        <v>-6.625389422492036</v>
       </c>
       <c r="D58">
-        <v>12.94893572972096</v>
+        <v>12.78591057750797</v>
       </c>
       <c r="E58">
-        <v>19.72040000000001</v>
+        <v>20.08130000000001</v>
       </c>
       <c r="F58">
-        <v>20.2104</v>
+        <v>20.5713</v>
       </c>
       <c r="G58">
         <v>1.16</v>
@@ -6037,37 +6037,37 @@
         <v>1.48</v>
       </c>
       <c r="M58">
-        <v>4.765612320000001</v>
+        <v>4.850712540000001</v>
       </c>
       <c r="N58">
-        <v>-3.285612320000001</v>
+        <v>-3.370712540000001</v>
       </c>
       <c r="O58">
-        <v>-0.8214030800000002</v>
+        <v>-0.8426781350000002</v>
       </c>
       <c r="P58">
-        <v>-2.464209240000001</v>
+        <v>-2.528034405000001</v>
       </c>
       <c r="Q58">
-        <v>-1.924209240000001</v>
+        <v>-1.988034405000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1659531241249266</v>
+        <v>0.1687473828255063</v>
       </c>
       <c r="T58">
-        <v>1.748374358146748</v>
+        <v>1.789034226940858</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07763955083950261</v>
+        <v>0.07627745345635344</v>
       </c>
       <c r="W58">
-        <v>0.2174925939120453</v>
+        <v>0.2178137764749919</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3105582033580104</v>
+        <v>0.3051098138254137</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1967152272057131</v>
+        <v>0.1986152272057131</v>
       </c>
       <c r="C59">
-        <v>-6.625389422492036</v>
+        <v>-7.145260688258391</v>
       </c>
       <c r="D59">
-        <v>12.78591057750797</v>
+        <v>12.62693931174161</v>
       </c>
       <c r="E59">
-        <v>20.08130000000001</v>
+        <v>20.44220000000001</v>
       </c>
       <c r="F59">
-        <v>20.5713</v>
+        <v>20.93220000000001</v>
       </c>
       <c r="G59">
         <v>1.16</v>
@@ -6119,37 +6119,37 @@
         <v>1.48</v>
       </c>
       <c r="M59">
-        <v>4.850712540000001</v>
+        <v>4.935812760000001</v>
       </c>
       <c r="N59">
-        <v>-3.370712540000001</v>
+        <v>-3.455812760000001</v>
       </c>
       <c r="O59">
-        <v>-0.8426781350000002</v>
+        <v>-0.8639531900000003</v>
       </c>
       <c r="P59">
-        <v>-2.528034405000001</v>
+        <v>-2.591859570000001</v>
       </c>
       <c r="Q59">
-        <v>-1.988034405000001</v>
+        <v>-2.051859570000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1687473828255063</v>
+        <v>0.1716747014642089</v>
       </c>
       <c r="T59">
-        <v>1.789034226940858</v>
+        <v>1.83163027996326</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07627745345635344</v>
+        <v>0.07496232494848526</v>
       </c>
       <c r="W59">
-        <v>0.2178137764749919</v>
+        <v>0.2181238837771472</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3051098138254137</v>
+        <v>0.299849299793941</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1986152272057131</v>
+        <v>0.2005152272057131</v>
       </c>
       <c r="C60">
-        <v>-7.145260688258391</v>
+        <v>-7.661227420380433</v>
       </c>
       <c r="D60">
-        <v>12.62693931174161</v>
+        <v>12.47187257961957</v>
       </c>
       <c r="E60">
-        <v>20.4422</v>
+        <v>20.8031</v>
       </c>
       <c r="F60">
-        <v>20.9322</v>
+        <v>21.2931</v>
       </c>
       <c r="G60">
         <v>1.16</v>
@@ -6201,37 +6201,37 @@
         <v>1.48</v>
       </c>
       <c r="M60">
-        <v>4.935812760000001</v>
+        <v>5.020912980000001</v>
       </c>
       <c r="N60">
-        <v>-3.455812760000001</v>
+        <v>-3.540912980000001</v>
       </c>
       <c r="O60">
-        <v>-0.8639531900000003</v>
+        <v>-0.8852282450000003</v>
       </c>
       <c r="P60">
-        <v>-2.591859570000001</v>
+        <v>-2.655684735000001</v>
       </c>
       <c r="Q60">
-        <v>-2.051859570000001</v>
+        <v>-2.115684735000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1716747014642088</v>
+        <v>0.1747448161340676</v>
       </c>
       <c r="T60">
-        <v>1.831630279963259</v>
+        <v>1.876304189230656</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07496232494848526</v>
+        <v>0.07369177706800246</v>
       </c>
       <c r="W60">
-        <v>0.2181238837771472</v>
+        <v>0.218423478967365</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.299849299793941</v>
+        <v>0.2947671082720098</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2005152272057131</v>
+        <v>0.2024152272057131</v>
       </c>
       <c r="C61">
-        <v>-7.661227420380433</v>
+        <v>-8.173431724081064</v>
       </c>
       <c r="D61">
-        <v>12.47187257961957</v>
+        <v>12.32056827591894</v>
       </c>
       <c r="E61">
-        <v>20.8031</v>
+        <v>21.164</v>
       </c>
       <c r="F61">
-        <v>21.2931</v>
+        <v>21.654</v>
       </c>
       <c r="G61">
         <v>1.16</v>
@@ -6283,37 +6283,37 @@
         <v>1.48</v>
       </c>
       <c r="M61">
-        <v>5.020912980000001</v>
+        <v>5.1060132</v>
       </c>
       <c r="N61">
-        <v>-3.540912980000001</v>
+        <v>-3.6260132</v>
       </c>
       <c r="O61">
-        <v>-0.8852282450000003</v>
+        <v>-0.9065033000000001</v>
       </c>
       <c r="P61">
-        <v>-2.655684735000001</v>
+        <v>-2.7195099</v>
       </c>
       <c r="Q61">
-        <v>-2.115684735000001</v>
+        <v>-2.1795099</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1747448161340676</v>
+        <v>0.1779684365374193</v>
       </c>
       <c r="T61">
-        <v>1.876304189230656</v>
+        <v>1.923211793961422</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07369177706800246</v>
+        <v>0.07246358078353576</v>
       </c>
       <c r="W61">
-        <v>0.218423478967365</v>
+        <v>0.2187130876512423</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2947671082720098</v>
+        <v>0.2898543231341431</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2024152272057131</v>
+        <v>0.2043152272057131</v>
       </c>
       <c r="C62">
-        <v>-8.173431724081064</v>
+        <v>-8.682008891359555</v>
       </c>
       <c r="D62">
-        <v>12.32056827591894</v>
+        <v>12.17289110864045</v>
       </c>
       <c r="E62">
-        <v>21.164</v>
+        <v>21.5249</v>
       </c>
       <c r="F62">
-        <v>21.654</v>
+        <v>22.0149</v>
       </c>
       <c r="G62">
         <v>1.16</v>
@@ -6365,37 +6365,37 @@
         <v>1.48</v>
       </c>
       <c r="M62">
-        <v>5.1060132</v>
+        <v>5.191113420000001</v>
       </c>
       <c r="N62">
-        <v>-3.6260132</v>
+        <v>-3.711113420000001</v>
       </c>
       <c r="O62">
-        <v>-0.9065033000000001</v>
+        <v>-0.9277783550000002</v>
       </c>
       <c r="P62">
-        <v>-2.7195099</v>
+        <v>-2.783335065000001</v>
       </c>
       <c r="Q62">
-        <v>-2.1795099</v>
+        <v>-2.243335065000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1779684365374193</v>
+        <v>0.1813573708076095</v>
       </c>
       <c r="T62">
-        <v>1.923211793961422</v>
+        <v>1.97252491688351</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07246358078353576</v>
+        <v>0.0712756532297073</v>
       </c>
       <c r="W62">
-        <v>0.2187130876512423</v>
+        <v>0.218993200968435</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2898543231341431</v>
+        <v>0.2851026129188292</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2043152272057131</v>
+        <v>0.2062152272057131</v>
       </c>
       <c r="C63">
-        <v>-8.682008891359555</v>
+        <v>-9.18708780447955</v>
       </c>
       <c r="D63">
-        <v>12.17289110864045</v>
+        <v>12.02871219552045</v>
       </c>
       <c r="E63">
-        <v>21.5249</v>
+        <v>21.8858</v>
       </c>
       <c r="F63">
-        <v>22.0149</v>
+        <v>22.3758</v>
       </c>
       <c r="G63">
         <v>1.16</v>
@@ -6447,37 +6447,37 @@
         <v>1.48</v>
       </c>
       <c r="M63">
-        <v>5.191113420000001</v>
+        <v>5.276213640000001</v>
       </c>
       <c r="N63">
-        <v>-3.711113420000001</v>
+        <v>-3.796213640000001</v>
       </c>
       <c r="O63">
-        <v>-0.9277783550000002</v>
+        <v>-0.9490534100000002</v>
       </c>
       <c r="P63">
-        <v>-2.783335065000001</v>
+        <v>-2.847160230000001</v>
       </c>
       <c r="Q63">
-        <v>-2.243335065000001</v>
+        <v>-2.30716023</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1813573708076095</v>
+        <v>0.1849246700393887</v>
       </c>
       <c r="T63">
-        <v>1.97252491688351</v>
+        <v>2.024433467327813</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0712756532297073</v>
+        <v>0.07012604591955074</v>
       </c>
       <c r="W63">
-        <v>0.218993200968435</v>
+        <v>0.2192642783721699</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2851026129188292</v>
+        <v>0.280504183678203</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2062152272057131</v>
+        <v>0.2081152272057131</v>
       </c>
       <c r="C64">
-        <v>-9.18708780447955</v>
+        <v>-9.688791311118663</v>
       </c>
       <c r="D64">
-        <v>12.02871219552045</v>
+        <v>11.88790868888134</v>
       </c>
       <c r="E64">
-        <v>21.8858</v>
+        <v>22.2467</v>
       </c>
       <c r="F64">
-        <v>22.3758</v>
+        <v>22.7367</v>
       </c>
       <c r="G64">
         <v>1.16</v>
@@ -6529,37 +6529,37 @@
         <v>1.48</v>
       </c>
       <c r="M64">
-        <v>5.276213640000001</v>
+        <v>5.361313860000001</v>
       </c>
       <c r="N64">
-        <v>-3.796213640000001</v>
+        <v>-3.881313860000001</v>
       </c>
       <c r="O64">
-        <v>-0.9490534100000002</v>
+        <v>-0.9703284650000003</v>
       </c>
       <c r="P64">
-        <v>-2.847160230000001</v>
+        <v>-2.910985395000001</v>
       </c>
       <c r="Q64">
-        <v>-2.30716023</v>
+        <v>-2.370985395000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1849246700393887</v>
+        <v>0.1886847962566695</v>
       </c>
       <c r="T64">
-        <v>2.024433467327813</v>
+        <v>2.0791478853637</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07012604591955074</v>
+        <v>0.06901293407955787</v>
       </c>
       <c r="W64">
-        <v>0.2192642783721699</v>
+        <v>0.2195267501440403</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.280504183678203</v>
+        <v>0.2760517363182314</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2081152272057131</v>
+        <v>0.2100152272057131</v>
       </c>
       <c r="C65">
-        <v>-9.688791311118663</v>
+        <v>-10.18723657347475</v>
       </c>
       <c r="D65">
-        <v>11.88790868888134</v>
+        <v>11.75036342652525</v>
       </c>
       <c r="E65">
-        <v>22.2467</v>
+        <v>22.60760000000001</v>
       </c>
       <c r="F65">
-        <v>22.7367</v>
+        <v>23.0976</v>
       </c>
       <c r="G65">
         <v>1.16</v>
@@ -6611,37 +6611,37 @@
         <v>1.48</v>
       </c>
       <c r="M65">
-        <v>5.361313860000001</v>
+        <v>5.446414080000001</v>
       </c>
       <c r="N65">
-        <v>-3.881313860000001</v>
+        <v>-3.966414080000001</v>
       </c>
       <c r="O65">
-        <v>-0.9703284650000003</v>
+        <v>-0.9916035200000003</v>
       </c>
       <c r="P65">
-        <v>-2.910985395000001</v>
+        <v>-2.974810560000001</v>
       </c>
       <c r="Q65">
-        <v>-2.370985395000001</v>
+        <v>-2.434810560000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1886847962566695</v>
+        <v>0.1926538183749103</v>
       </c>
       <c r="T65">
-        <v>2.0791478853637</v>
+        <v>2.136901993290469</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06901293407955787</v>
+        <v>0.06793460698456477</v>
       </c>
       <c r="W65">
-        <v>0.2195267501440403</v>
+        <v>0.2197810196730396</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2760517363182314</v>
+        <v>0.2717384279382591</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2100152272057131</v>
+        <v>0.2119152272057131</v>
       </c>
       <c r="C66">
-        <v>-10.18723657347475</v>
+        <v>-10.68253539341406</v>
       </c>
       <c r="D66">
-        <v>11.75036342652525</v>
+        <v>11.61596460658594</v>
       </c>
       <c r="E66">
-        <v>22.60760000000001</v>
+        <v>22.96850000000001</v>
       </c>
       <c r="F66">
-        <v>23.0976</v>
+        <v>23.4585</v>
       </c>
       <c r="G66">
         <v>1.16</v>
@@ -6693,37 +6693,37 @@
         <v>1.48</v>
       </c>
       <c r="M66">
-        <v>5.446414080000001</v>
+        <v>5.531514300000001</v>
       </c>
       <c r="N66">
-        <v>-3.966414080000001</v>
+        <v>-4.051514300000001</v>
       </c>
       <c r="O66">
-        <v>-0.9916035200000003</v>
+        <v>-1.012878575</v>
       </c>
       <c r="P66">
-        <v>-2.974810560000001</v>
+        <v>-3.038635725000001</v>
       </c>
       <c r="Q66">
-        <v>-2.434810560000001</v>
+        <v>-2.498635725000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1926538183749103</v>
+        <v>0.1968496417570506</v>
       </c>
       <c r="T66">
-        <v>2.136901993290469</v>
+        <v>2.197956335955912</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06793460698456477</v>
+        <v>0.06688945918480224</v>
       </c>
       <c r="W66">
-        <v>0.2197810196730396</v>
+        <v>0.2200274655242236</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2717384279382591</v>
+        <v>0.2675578367392091</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2119152272057131</v>
+        <v>0.2138152272057131</v>
       </c>
       <c r="C67">
-        <v>-10.68253539341406</v>
+        <v>-11.17479451555774</v>
       </c>
       <c r="D67">
-        <v>11.61596460658594</v>
+        <v>11.48460548444226</v>
       </c>
       <c r="E67">
-        <v>22.96850000000001</v>
+        <v>23.3294</v>
       </c>
       <c r="F67">
-        <v>23.4585</v>
+        <v>23.8194</v>
       </c>
       <c r="G67">
         <v>1.16</v>
@@ -6775,37 +6775,37 @@
         <v>1.48</v>
       </c>
       <c r="M67">
-        <v>5.531514300000001</v>
+        <v>5.616614520000001</v>
       </c>
       <c r="N67">
-        <v>-4.051514300000001</v>
+        <v>-4.13661452</v>
       </c>
       <c r="O67">
-        <v>-1.012878575</v>
+        <v>-1.03415363</v>
       </c>
       <c r="P67">
-        <v>-3.038635725000001</v>
+        <v>-3.10246089</v>
       </c>
       <c r="Q67">
-        <v>-2.498635725000001</v>
+        <v>-2.56246089</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1968496417570506</v>
+        <v>0.2012922782793168</v>
       </c>
       <c r="T67">
-        <v>2.197956335955912</v>
+        <v>2.26260211054285</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06688945918480224</v>
+        <v>0.06587598253048706</v>
       </c>
       <c r="W67">
-        <v>0.2200274655242236</v>
+        <v>0.2202664433193111</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2675578367392091</v>
+        <v>0.2635039301219483</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2138152272057131</v>
+        <v>0.2157152272057131</v>
       </c>
       <c r="C68">
-        <v>-11.17479451555774</v>
+        <v>-11.6641159100336</v>
       </c>
       <c r="D68">
-        <v>11.48460548444226</v>
+        <v>11.3561840899664</v>
       </c>
       <c r="E68">
-        <v>23.3294</v>
+        <v>23.6903</v>
       </c>
       <c r="F68">
-        <v>23.8194</v>
+        <v>24.1803</v>
       </c>
       <c r="G68">
         <v>1.16</v>
@@ -6857,37 +6857,37 @@
         <v>1.48</v>
       </c>
       <c r="M68">
-        <v>5.616614520000001</v>
+        <v>5.701714740000001</v>
       </c>
       <c r="N68">
-        <v>-4.13661452</v>
+        <v>-4.221714740000001</v>
       </c>
       <c r="O68">
-        <v>-1.03415363</v>
+        <v>-1.055428685</v>
       </c>
       <c r="P68">
-        <v>-3.10246089</v>
+        <v>-3.166286055000001</v>
       </c>
       <c r="Q68">
-        <v>-2.56246089</v>
+        <v>-2.626286055000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2012922782793168</v>
+        <v>0.2060041654999022</v>
       </c>
       <c r="T68">
-        <v>2.26260211054285</v>
+        <v>2.331165810862331</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06587598253048706</v>
+        <v>0.06489275891062904</v>
       </c>
       <c r="W68">
-        <v>0.2202664433193111</v>
+        <v>0.2204982874488737</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2635039301219483</v>
+        <v>0.259571035642516</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2157152272057131</v>
+        <v>0.2176152272057131</v>
       </c>
       <c r="C69">
-        <v>-11.6641159100336</v>
+        <v>-12.15059703646719</v>
       </c>
       <c r="D69">
-        <v>11.3561840899664</v>
+        <v>11.23060296353281</v>
       </c>
       <c r="E69">
-        <v>23.6903</v>
+        <v>24.05120000000001</v>
       </c>
       <c r="F69">
-        <v>24.1803</v>
+        <v>24.5412</v>
       </c>
       <c r="G69">
         <v>1.16</v>
@@ -6939,37 +6939,37 @@
         <v>1.48</v>
       </c>
       <c r="M69">
-        <v>5.701714740000001</v>
+        <v>5.786814960000001</v>
       </c>
       <c r="N69">
-        <v>-4.221714740000001</v>
+        <v>-4.306814960000001</v>
       </c>
       <c r="O69">
-        <v>-1.055428685</v>
+        <v>-1.07670374</v>
       </c>
       <c r="P69">
-        <v>-3.166286055000001</v>
+        <v>-3.23011122</v>
       </c>
       <c r="Q69">
-        <v>-2.626286055000001</v>
+        <v>-2.69011122</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2060041654999022</v>
+        <v>0.2110105456717741</v>
       </c>
       <c r="T69">
-        <v>2.331165810862331</v>
+        <v>2.404014742451778</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06489275891062904</v>
+        <v>0.06393845363253155</v>
       </c>
       <c r="W69">
-        <v>0.2204982874488737</v>
+        <v>0.220723312633449</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.259571035642516</v>
+        <v>0.2557538145301262</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2176152272057131</v>
+        <v>0.2195152272057131</v>
       </c>
       <c r="C70">
-        <v>-12.15059703646719</v>
+        <v>-12.63433109064854</v>
       </c>
       <c r="D70">
-        <v>11.23060296353281</v>
+        <v>11.10776890935146</v>
       </c>
       <c r="E70">
-        <v>24.05120000000001</v>
+        <v>24.41210000000001</v>
       </c>
       <c r="F70">
-        <v>24.5412</v>
+        <v>24.9021</v>
       </c>
       <c r="G70">
         <v>1.16</v>
@@ -7021,37 +7021,37 @@
         <v>1.48</v>
       </c>
       <c r="M70">
-        <v>5.786814960000001</v>
+        <v>5.871915180000001</v>
       </c>
       <c r="N70">
-        <v>-4.306814960000001</v>
+        <v>-4.391915180000002</v>
       </c>
       <c r="O70">
-        <v>-1.07670374</v>
+        <v>-1.097978795</v>
       </c>
       <c r="P70">
-        <v>-3.23011122</v>
+        <v>-3.293936385000001</v>
       </c>
       <c r="Q70">
-        <v>-2.69011122</v>
+        <v>-2.753936385000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2110105456717741</v>
+        <v>0.2163399181127991</v>
       </c>
       <c r="T70">
-        <v>2.404014742451778</v>
+        <v>2.481563605111513</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06393845363253155</v>
+        <v>0.06301180937698761</v>
       </c>
       <c r="W70">
-        <v>0.220723312633449</v>
+        <v>0.2209418153489063</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2557538145301262</v>
+        <v>0.2520472375079504</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2195152272057131</v>
+        <v>0.2214152272057131</v>
       </c>
       <c r="C71">
-        <v>-12.63433109064854</v>
+        <v>-13.11540723518666</v>
       </c>
       <c r="D71">
-        <v>11.10776890935146</v>
+        <v>10.98759276481335</v>
       </c>
       <c r="E71">
-        <v>24.41210000000001</v>
+        <v>24.77300000000001</v>
       </c>
       <c r="F71">
-        <v>24.9021</v>
+        <v>25.26300000000001</v>
       </c>
       <c r="G71">
         <v>1.16</v>
@@ -7103,37 +7103,37 @@
         <v>1.48</v>
       </c>
       <c r="M71">
-        <v>5.871915180000001</v>
+        <v>5.957015400000001</v>
       </c>
       <c r="N71">
-        <v>-4.391915180000002</v>
+        <v>-4.477015400000001</v>
       </c>
       <c r="O71">
-        <v>-1.097978795</v>
+        <v>-1.11925385</v>
       </c>
       <c r="P71">
-        <v>-3.293936385000001</v>
+        <v>-3.357761550000001</v>
       </c>
       <c r="Q71">
-        <v>-2.753936385000001</v>
+        <v>-2.817761550000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2163399181127991</v>
+        <v>0.2220245820498924</v>
       </c>
       <c r="T71">
-        <v>2.481563605111513</v>
+        <v>2.564282391948564</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06301180937698761</v>
+        <v>0.06211164067160208</v>
       </c>
       <c r="W71">
-        <v>0.2209418153489063</v>
+        <v>0.2211540751296363</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2520472375079504</v>
+        <v>0.2484465626864084</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2214152272057131</v>
+        <v>0.2233152272057131</v>
       </c>
       <c r="C72">
-        <v>-13.11540723518666</v>
+        <v>-13.59391081535138</v>
       </c>
       <c r="D72">
-        <v>10.98759276481335</v>
+        <v>10.86998918464863</v>
       </c>
       <c r="E72">
-        <v>24.77300000000001</v>
+        <v>25.13390000000001</v>
       </c>
       <c r="F72">
-        <v>25.26300000000001</v>
+        <v>25.62390000000001</v>
       </c>
       <c r="G72">
         <v>1.16</v>
@@ -7185,37 +7185,37 @@
         <v>1.48</v>
       </c>
       <c r="M72">
-        <v>5.957015400000001</v>
+        <v>6.042115620000001</v>
       </c>
       <c r="N72">
-        <v>-4.477015400000001</v>
+        <v>-4.562115620000002</v>
       </c>
       <c r="O72">
-        <v>-1.11925385</v>
+        <v>-1.140528905</v>
       </c>
       <c r="P72">
-        <v>-3.357761550000001</v>
+        <v>-3.421586715000001</v>
       </c>
       <c r="Q72">
-        <v>-2.817761550000001</v>
+        <v>-2.881586715000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2220245820498924</v>
+        <v>0.2281012917757508</v>
       </c>
       <c r="T72">
-        <v>2.564282391948564</v>
+        <v>2.652705922705411</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06211164067160208</v>
+        <v>0.06123682883115698</v>
       </c>
       <c r="W72">
-        <v>0.2211540751296363</v>
+        <v>0.2213603557616132</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2484465626864084</v>
+        <v>0.2449473153246279</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2233152272057131</v>
+        <v>0.225215227205713</v>
       </c>
       <c r="C73">
-        <v>-13.59391081535138</v>
+        <v>-14.06992356120071</v>
       </c>
       <c r="D73">
-        <v>10.86998918464863</v>
+        <v>10.75487643879929</v>
       </c>
       <c r="E73">
-        <v>25.1339</v>
+        <v>25.4948</v>
       </c>
       <c r="F73">
-        <v>25.6239</v>
+        <v>25.9848</v>
       </c>
       <c r="G73">
         <v>1.16</v>
@@ -7267,37 +7267,37 @@
         <v>1.48</v>
       </c>
       <c r="M73">
-        <v>6.042115620000001</v>
+        <v>6.12721584</v>
       </c>
       <c r="N73">
-        <v>-4.56211562</v>
+        <v>-4.647215839999999</v>
       </c>
       <c r="O73">
-        <v>-1.140528905</v>
+        <v>-1.16180396</v>
       </c>
       <c r="P73">
-        <v>-3.421586715</v>
+        <v>-3.48541188</v>
       </c>
       <c r="Q73">
-        <v>-2.881586715</v>
+        <v>-2.94541188</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2281012917757507</v>
+        <v>0.2346120521963132</v>
       </c>
       <c r="T73">
-        <v>2.65270592270541</v>
+        <v>2.747445419944889</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06123682883115698</v>
+        <v>0.06038631731961314</v>
       </c>
       <c r="W73">
-        <v>0.2213603557616132</v>
+        <v>0.2215609063760352</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.244947315324628</v>
+        <v>0.2415452692784527</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.225215227205713</v>
+        <v>0.2271152272057131</v>
       </c>
       <c r="C74">
-        <v>-14.06992356120071</v>
+        <v>-14.54352377699966</v>
       </c>
       <c r="D74">
-        <v>10.75487643879929</v>
+        <v>10.64217622300034</v>
       </c>
       <c r="E74">
-        <v>25.4948</v>
+        <v>25.8557</v>
       </c>
       <c r="F74">
-        <v>25.9848</v>
+        <v>26.3457</v>
       </c>
       <c r="G74">
         <v>1.16</v>
@@ -7349,37 +7349,37 @@
         <v>1.48</v>
       </c>
       <c r="M74">
-        <v>6.12721584</v>
+        <v>6.21231606</v>
       </c>
       <c r="N74">
-        <v>-4.647215839999999</v>
+        <v>-4.73231606</v>
       </c>
       <c r="O74">
-        <v>-1.16180396</v>
+        <v>-1.183079015</v>
       </c>
       <c r="P74">
-        <v>-3.48541188</v>
+        <v>-3.549237045</v>
       </c>
       <c r="Q74">
-        <v>-2.94541188</v>
+        <v>-3.009237045</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2346120521963132</v>
+        <v>0.241605091166547</v>
       </c>
       <c r="T74">
-        <v>2.747445419944889</v>
+        <v>2.849202657720626</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06038631731961314</v>
+        <v>0.05955910749331707</v>
       </c>
       <c r="W74">
-        <v>0.2215609063760352</v>
+        <v>0.2217559624530759</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2415452692784527</v>
+        <v>0.2382364299732682</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2271152272057131</v>
+        <v>0.229015227205713</v>
       </c>
       <c r="C75">
-        <v>-14.54352377699966</v>
+        <v>-15.01478651885298</v>
       </c>
       <c r="D75">
-        <v>10.64217622300034</v>
+        <v>10.53181348114703</v>
       </c>
       <c r="E75">
-        <v>25.8557</v>
+        <v>26.2166</v>
       </c>
       <c r="F75">
-        <v>26.3457</v>
+        <v>26.7066</v>
       </c>
       <c r="G75">
         <v>1.16</v>
@@ -7431,37 +7431,37 @@
         <v>1.48</v>
       </c>
       <c r="M75">
-        <v>6.21231606</v>
+        <v>6.297416280000001</v>
       </c>
       <c r="N75">
-        <v>-4.73231606</v>
+        <v>-4.817416280000002</v>
       </c>
       <c r="O75">
-        <v>-1.183079015</v>
+        <v>-1.20435407</v>
       </c>
       <c r="P75">
-        <v>-3.549237045</v>
+        <v>-3.613062210000001</v>
       </c>
       <c r="Q75">
-        <v>-3.009237045</v>
+        <v>-3.073062210000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.241605091166547</v>
+        <v>0.2491360562114142</v>
       </c>
       <c r="T75">
-        <v>2.849202657720626</v>
+        <v>2.958787375325265</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05955910749331707</v>
+        <v>0.05875425468935332</v>
       </c>
       <c r="W75">
-        <v>0.2217559624530759</v>
+        <v>0.2219457467442505</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2382364299732682</v>
+        <v>0.2350170187574132</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.229015227205713</v>
+        <v>0.2309152272057131</v>
       </c>
       <c r="C76">
-        <v>-15.01478651885298</v>
+        <v>-15.48378376139879</v>
       </c>
       <c r="D76">
-        <v>10.53181348114703</v>
+        <v>10.42371623860121</v>
       </c>
       <c r="E76">
-        <v>26.2166</v>
+        <v>26.5775</v>
       </c>
       <c r="F76">
-        <v>26.7066</v>
+        <v>27.0675</v>
       </c>
       <c r="G76">
         <v>1.16</v>
@@ -7513,37 +7513,37 @@
         <v>1.48</v>
       </c>
       <c r="M76">
-        <v>6.297416280000001</v>
+        <v>6.382516500000001</v>
       </c>
       <c r="N76">
-        <v>-4.817416280000002</v>
+        <v>-4.902516500000001</v>
       </c>
       <c r="O76">
-        <v>-1.20435407</v>
+        <v>-1.225629125</v>
       </c>
       <c r="P76">
-        <v>-3.613062210000001</v>
+        <v>-3.676887375000001</v>
       </c>
       <c r="Q76">
-        <v>-3.073062210000001</v>
+        <v>-3.136887375000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2491360562114142</v>
+        <v>0.2572694984598708</v>
       </c>
       <c r="T76">
-        <v>2.958787375325265</v>
+        <v>3.077138870338276</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05875425468935332</v>
+        <v>0.05797086462682861</v>
       </c>
       <c r="W76">
-        <v>0.2219457467442505</v>
+        <v>0.2221304701209938</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2350170187574132</v>
+        <v>0.2318834585073145</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2309152272057131</v>
+        <v>0.2328152272057131</v>
       </c>
       <c r="C77">
-        <v>-15.48378376139879</v>
+        <v>-15.95058455434094</v>
       </c>
       <c r="D77">
-        <v>10.42371623860121</v>
+        <v>10.31781544565906</v>
       </c>
       <c r="E77">
-        <v>26.5775</v>
+        <v>26.93840000000001</v>
       </c>
       <c r="F77">
-        <v>27.0675</v>
+        <v>27.4284</v>
       </c>
       <c r="G77">
         <v>1.16</v>
@@ -7595,37 +7595,37 @@
         <v>1.48</v>
       </c>
       <c r="M77">
-        <v>6.382516500000001</v>
+        <v>6.467616720000001</v>
       </c>
       <c r="N77">
-        <v>-4.902516500000001</v>
+        <v>-4.987616720000002</v>
       </c>
       <c r="O77">
-        <v>-1.225629125</v>
+        <v>-1.24690418</v>
       </c>
       <c r="P77">
-        <v>-3.676887375000001</v>
+        <v>-3.740712540000001</v>
       </c>
       <c r="Q77">
-        <v>-3.136887375000001</v>
+        <v>-3.200712540000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2572694984598708</v>
+        <v>0.2660807275623654</v>
       </c>
       <c r="T77">
-        <v>3.077138870338276</v>
+        <v>3.205352989935704</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05797086462682861</v>
+        <v>0.05720809009226507</v>
       </c>
       <c r="W77">
-        <v>0.2221304701209938</v>
+        <v>0.2223103323562439</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2318834585073145</v>
+        <v>0.2288323603690602</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2328152272057131</v>
+        <v>0.2347152272057131</v>
       </c>
       <c r="C78">
-        <v>-15.95058455434094</v>
+        <v>-16.41525516953548</v>
       </c>
       <c r="D78">
-        <v>10.31781544565906</v>
+        <v>10.21404483046453</v>
       </c>
       <c r="E78">
-        <v>26.93840000000001</v>
+        <v>27.29930000000001</v>
       </c>
       <c r="F78">
-        <v>27.4284</v>
+        <v>27.7893</v>
       </c>
       <c r="G78">
         <v>1.16</v>
@@ -7677,37 +7677,37 @@
         <v>1.48</v>
       </c>
       <c r="M78">
-        <v>6.467616720000001</v>
+        <v>6.552716940000002</v>
       </c>
       <c r="N78">
-        <v>-4.987616720000002</v>
+        <v>-5.072716940000001</v>
       </c>
       <c r="O78">
-        <v>-1.24690418</v>
+        <v>-1.268179235</v>
       </c>
       <c r="P78">
-        <v>-3.740712540000001</v>
+        <v>-3.804537705000001</v>
       </c>
       <c r="Q78">
-        <v>-3.200712540000001</v>
+        <v>-3.264537705000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2660807275623654</v>
+        <v>0.2756581504998596</v>
       </c>
       <c r="T78">
-        <v>3.205352989935704</v>
+        <v>3.34471616341117</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05720809009226507</v>
+        <v>0.05646512788327462</v>
       </c>
       <c r="W78">
-        <v>0.2223103323562439</v>
+        <v>0.2224855228451239</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2288323603690602</v>
+        <v>0.2258605115330985</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2347152272057131</v>
+        <v>0.2366152272057131</v>
       </c>
       <c r="C79">
-        <v>-16.41525516953548</v>
+        <v>-16.87785923928963</v>
       </c>
       <c r="D79">
-        <v>10.21404483046453</v>
+        <v>10.11234076071038</v>
       </c>
       <c r="E79">
-        <v>27.29930000000001</v>
+        <v>27.66020000000001</v>
       </c>
       <c r="F79">
-        <v>27.7893</v>
+        <v>28.15020000000001</v>
       </c>
       <c r="G79">
         <v>1.16</v>
@@ -7759,37 +7759,37 @@
         <v>1.48</v>
       </c>
       <c r="M79">
-        <v>6.552716940000002</v>
+        <v>6.637817160000002</v>
       </c>
       <c r="N79">
-        <v>-5.072716940000001</v>
+        <v>-5.157817160000002</v>
       </c>
       <c r="O79">
-        <v>-1.268179235</v>
+        <v>-1.289454290000001</v>
       </c>
       <c r="P79">
-        <v>-3.804537705000001</v>
+        <v>-3.868362870000002</v>
       </c>
       <c r="Q79">
-        <v>-3.264537705000001</v>
+        <v>-3.328362870000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2756581504998596</v>
+        <v>0.2861062482498533</v>
       </c>
       <c r="T79">
-        <v>3.34471616341117</v>
+        <v>3.496748716293496</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05646512788327462</v>
+        <v>0.0557412159873352</v>
       </c>
       <c r="W79">
-        <v>0.2224855228451239</v>
+        <v>0.2226562212701864</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2258605115330985</v>
+        <v>0.2229648639493407</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2366152272057131</v>
+        <v>0.2385152272057131</v>
       </c>
       <c r="C80">
-        <v>-16.87785923928963</v>
+        <v>-17.33845788647976</v>
       </c>
       <c r="D80">
-        <v>10.11234076071038</v>
+        <v>10.01264211352025</v>
       </c>
       <c r="E80">
-        <v>27.66020000000001</v>
+        <v>28.0211</v>
       </c>
       <c r="F80">
-        <v>28.15020000000001</v>
+        <v>28.5111</v>
       </c>
       <c r="G80">
         <v>1.16</v>
@@ -7841,37 +7841,37 @@
         <v>1.48</v>
       </c>
       <c r="M80">
-        <v>6.637817160000002</v>
+        <v>6.722917380000001</v>
       </c>
       <c r="N80">
-        <v>-5.157817160000002</v>
+        <v>-5.242917380000002</v>
       </c>
       <c r="O80">
-        <v>-1.289454290000001</v>
+        <v>-1.310729345</v>
       </c>
       <c r="P80">
-        <v>-3.868362870000002</v>
+        <v>-3.932188035000001</v>
       </c>
       <c r="Q80">
-        <v>-3.328362870000002</v>
+        <v>-3.392188035000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2861062482498533</v>
+        <v>0.2975494029284176</v>
       </c>
       <c r="T80">
-        <v>3.496748716293496</v>
+        <v>3.663260559926519</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0557412159873352</v>
+        <v>0.05503563097483729</v>
       </c>
       <c r="W80">
-        <v>0.2226562212701864</v>
+        <v>0.2228225982161334</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2229648639493407</v>
+        <v>0.2201425238993491</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2385152272057131</v>
+        <v>0.2404152272057131</v>
       </c>
       <c r="C81">
-        <v>-17.33845788647976</v>
+        <v>-17.79710984704747</v>
       </c>
       <c r="D81">
-        <v>10.01264211352025</v>
+        <v>9.914890152952536</v>
       </c>
       <c r="E81">
-        <v>28.0211</v>
+        <v>28.38200000000001</v>
       </c>
       <c r="F81">
-        <v>28.5111</v>
+        <v>28.872</v>
       </c>
       <c r="G81">
         <v>1.16</v>
@@ -7923,37 +7923,37 @@
         <v>1.48</v>
       </c>
       <c r="M81">
-        <v>6.722917380000001</v>
+        <v>6.808017600000001</v>
       </c>
       <c r="N81">
-        <v>-5.242917380000002</v>
+        <v>-5.328017600000001</v>
       </c>
       <c r="O81">
-        <v>-1.310729345</v>
+        <v>-1.3320044</v>
       </c>
       <c r="P81">
-        <v>-3.932188035000001</v>
+        <v>-3.996013200000001</v>
       </c>
       <c r="Q81">
-        <v>-3.392188035000001</v>
+        <v>-3.456013200000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2975494029284176</v>
+        <v>0.3101368730748386</v>
       </c>
       <c r="T81">
-        <v>3.663260559926519</v>
+        <v>3.846423587922846</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05503563097483729</v>
+        <v>0.05434768558765182</v>
       </c>
       <c r="W81">
-        <v>0.2228225982161334</v>
+        <v>0.2229848157384317</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2201425238993491</v>
+        <v>0.2173907423506073</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2404152272057131</v>
+        <v>0.2423152272057131</v>
       </c>
       <c r="C82">
-        <v>-17.79710984704747</v>
+        <v>-18.25387158538945</v>
       </c>
       <c r="D82">
-        <v>9.914890152952536</v>
+        <v>9.819028414610555</v>
       </c>
       <c r="E82">
-        <v>28.38200000000001</v>
+        <v>28.74290000000001</v>
       </c>
       <c r="F82">
-        <v>28.872</v>
+        <v>29.2329</v>
       </c>
       <c r="G82">
         <v>1.16</v>
@@ -8005,37 +8005,37 @@
         <v>1.48</v>
       </c>
       <c r="M82">
-        <v>6.808017600000001</v>
+        <v>6.893117820000001</v>
       </c>
       <c r="N82">
-        <v>-5.328017600000001</v>
+        <v>-5.413117820000002</v>
       </c>
       <c r="O82">
-        <v>-1.3320044</v>
+        <v>-1.353279455</v>
       </c>
       <c r="P82">
-        <v>-3.996013200000001</v>
+        <v>-4.059838365000001</v>
       </c>
       <c r="Q82">
-        <v>-3.456013200000001</v>
+        <v>-3.519838365000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3101368730748386</v>
+        <v>0.3240493400787774</v>
       </c>
       <c r="T82">
-        <v>3.846423587922846</v>
+        <v>4.048866934655627</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05434768558765182</v>
+        <v>0.05367672650632278</v>
       </c>
       <c r="W82">
-        <v>0.2229848157384317</v>
+        <v>0.2231430278898091</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2173907423506073</v>
+        <v>0.2147069060252911</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2423152272057131</v>
+        <v>0.2442152272057131</v>
       </c>
       <c r="C83">
-        <v>-18.25387158538945</v>
+        <v>-18.70879740311774</v>
       </c>
       <c r="D83">
-        <v>9.819028414610555</v>
+        <v>9.725002596882266</v>
       </c>
       <c r="E83">
-        <v>28.74290000000001</v>
+        <v>29.10380000000001</v>
       </c>
       <c r="F83">
-        <v>29.2329</v>
+        <v>29.59380000000001</v>
       </c>
       <c r="G83">
         <v>1.16</v>
@@ -8087,37 +8087,37 @@
         <v>1.48</v>
       </c>
       <c r="M83">
-        <v>6.893117820000001</v>
+        <v>6.978218040000002</v>
       </c>
       <c r="N83">
-        <v>-5.413117820000002</v>
+        <v>-5.498218040000001</v>
       </c>
       <c r="O83">
-        <v>-1.353279455</v>
+        <v>-1.37455451</v>
       </c>
       <c r="P83">
-        <v>-4.059838365000001</v>
+        <v>-4.123663530000001</v>
       </c>
       <c r="Q83">
-        <v>-3.519838365000001</v>
+        <v>-3.583663530000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3240493400787774</v>
+        <v>0.3395076367498207</v>
       </c>
       <c r="T83">
-        <v>4.048866934655627</v>
+        <v>4.273803986580941</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05367672650632278</v>
+        <v>0.05302213228063592</v>
       </c>
       <c r="W83">
-        <v>0.2231430278898091</v>
+        <v>0.2232973812082261</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2147069060252911</v>
+        <v>0.2120885291225437</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2442152272057131</v>
+        <v>0.2461152272057131</v>
       </c>
       <c r="C84">
-        <v>-18.70879740311774</v>
+        <v>-19.16193954163025</v>
       </c>
       <c r="D84">
-        <v>9.725002596882266</v>
+        <v>9.63276045836975</v>
       </c>
       <c r="E84">
-        <v>29.10380000000001</v>
+        <v>29.46470000000001</v>
       </c>
       <c r="F84">
-        <v>29.59380000000001</v>
+        <v>29.95470000000001</v>
       </c>
       <c r="G84">
         <v>1.16</v>
@@ -8169,37 +8169,37 @@
         <v>1.48</v>
       </c>
       <c r="M84">
-        <v>6.978218040000002</v>
+        <v>7.063318260000002</v>
       </c>
       <c r="N84">
-        <v>-5.498218040000001</v>
+        <v>-5.583318260000002</v>
       </c>
       <c r="O84">
-        <v>-1.37455451</v>
+        <v>-1.395829565000001</v>
       </c>
       <c r="P84">
-        <v>-4.123663530000001</v>
+        <v>-4.187488695000002</v>
       </c>
       <c r="Q84">
-        <v>-3.583663530000001</v>
+        <v>-3.647488695000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3395076367498207</v>
+        <v>0.3567845565586337</v>
       </c>
       <c r="T84">
-        <v>4.273803986580941</v>
+        <v>4.525204221085701</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05302213228063592</v>
+        <v>0.05238331140978488</v>
       </c>
       <c r="W84">
-        <v>0.2232973812082261</v>
+        <v>0.2234480151695727</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2120885291225437</v>
+        <v>0.2095332456391394</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2461152272057131</v>
+        <v>0.2480152272057131</v>
       </c>
       <c r="C85">
-        <v>-19.16193954163025</v>
+        <v>-19.613348278899</v>
       </c>
       <c r="D85">
-        <v>9.63276045836975</v>
+        <v>9.542251721101001</v>
       </c>
       <c r="E85">
-        <v>29.46470000000001</v>
+        <v>29.82560000000001</v>
       </c>
       <c r="F85">
-        <v>29.95470000000001</v>
+        <v>30.31560000000001</v>
       </c>
       <c r="G85">
         <v>1.16</v>
@@ -8251,37 +8251,37 @@
         <v>1.48</v>
       </c>
       <c r="M85">
-        <v>7.063318260000002</v>
+        <v>7.148418480000002</v>
       </c>
       <c r="N85">
-        <v>-5.583318260000002</v>
+        <v>-5.668418480000001</v>
       </c>
       <c r="O85">
-        <v>-1.395829565000001</v>
+        <v>-1.41710462</v>
       </c>
       <c r="P85">
-        <v>-4.187488695000002</v>
+        <v>-4.251313860000002</v>
       </c>
       <c r="Q85">
-        <v>-3.647488695000002</v>
+        <v>-3.711313860000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3567845565586337</v>
+        <v>0.3762210913435484</v>
       </c>
       <c r="T85">
-        <v>4.525204221085701</v>
+        <v>4.808029484903559</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05238331140978488</v>
+        <v>0.05175970055966839</v>
       </c>
       <c r="W85">
-        <v>0.2234480151695727</v>
+        <v>0.2235950626080302</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2095332456391394</v>
+        <v>0.2070388022386737</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2480152272057131</v>
+        <v>0.2499152272057131</v>
       </c>
       <c r="C86">
-        <v>-19.613348278899</v>
+        <v>-20.06307202085246</v>
       </c>
       <c r="D86">
-        <v>9.542251721100998</v>
+        <v>9.453427979147538</v>
       </c>
       <c r="E86">
-        <v>29.8256</v>
+        <v>30.1865</v>
       </c>
       <c r="F86">
-        <v>30.3156</v>
+        <v>30.6765</v>
       </c>
       <c r="G86">
         <v>1.16</v>
@@ -8333,37 +8333,37 @@
         <v>1.48</v>
       </c>
       <c r="M86">
-        <v>7.148418480000001</v>
+        <v>7.2335187</v>
       </c>
       <c r="N86">
-        <v>-5.668418480000001</v>
+        <v>-5.753518700000001</v>
       </c>
       <c r="O86">
-        <v>-1.41710462</v>
+        <v>-1.438379675</v>
       </c>
       <c r="P86">
-        <v>-4.251313860000002</v>
+        <v>-4.315139025000001</v>
       </c>
       <c r="Q86">
-        <v>-3.711313860000002</v>
+        <v>-3.775139025000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3762210913435481</v>
+        <v>0.3982491640997847</v>
       </c>
       <c r="T86">
-        <v>4.808029484903555</v>
+        <v>5.128564783897126</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0517597005596684</v>
+        <v>0.05115076290602525</v>
       </c>
       <c r="W86">
-        <v>0.2235950626080302</v>
+        <v>0.2237386501067593</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2070388022386735</v>
+        <v>0.204603051624101</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2499152272057131</v>
+        <v>0.251815227205713</v>
       </c>
       <c r="C87">
-        <v>-20.06307202085246</v>
+        <v>-20.51115738770132</v>
       </c>
       <c r="D87">
-        <v>9.453427979147538</v>
+        <v>9.366242612298683</v>
       </c>
       <c r="E87">
-        <v>30.1865</v>
+        <v>30.5474</v>
       </c>
       <c r="F87">
-        <v>30.6765</v>
+        <v>31.0374</v>
       </c>
       <c r="G87">
         <v>1.16</v>
@@ -8415,37 +8415,37 @@
         <v>1.48</v>
       </c>
       <c r="M87">
-        <v>7.2335187</v>
+        <v>7.31861892</v>
       </c>
       <c r="N87">
-        <v>-5.753518700000001</v>
+        <v>-5.83861892</v>
       </c>
       <c r="O87">
-        <v>-1.438379675</v>
+        <v>-1.45965473</v>
       </c>
       <c r="P87">
-        <v>-4.315139025000001</v>
+        <v>-4.37896419</v>
       </c>
       <c r="Q87">
-        <v>-3.775139025000001</v>
+        <v>-3.83896419</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3982491640997847</v>
+        <v>0.4234241043926265</v>
       </c>
       <c r="T87">
-        <v>5.128564783897126</v>
+        <v>5.494890839889778</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05115076290602525</v>
+        <v>0.05055598659316449</v>
       </c>
       <c r="W87">
-        <v>0.2237386501067593</v>
+        <v>0.2238788983613318</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.204603051624101</v>
+        <v>0.2022239463726581</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.251815227205713</v>
+        <v>0.2537152272057131</v>
       </c>
       <c r="C88">
-        <v>-20.51115738770132</v>
+        <v>-20.95764929553095</v>
       </c>
       <c r="D88">
-        <v>9.366242612298683</v>
+        <v>9.280650704469052</v>
       </c>
       <c r="E88">
-        <v>30.5474</v>
+        <v>30.9083</v>
       </c>
       <c r="F88">
-        <v>31.0374</v>
+        <v>31.3983</v>
       </c>
       <c r="G88">
         <v>1.16</v>
@@ -8497,37 +8497,37 @@
         <v>1.48</v>
       </c>
       <c r="M88">
-        <v>7.31861892</v>
+        <v>7.403719140000001</v>
       </c>
       <c r="N88">
-        <v>-5.83861892</v>
+        <v>-5.923719140000001</v>
       </c>
       <c r="O88">
-        <v>-1.45965473</v>
+        <v>-1.480929785</v>
       </c>
       <c r="P88">
-        <v>-4.37896419</v>
+        <v>-4.442789355</v>
       </c>
       <c r="Q88">
-        <v>-3.83896419</v>
+        <v>-3.902789355</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4234241043926265</v>
+        <v>0.4524721124228285</v>
       </c>
       <c r="T88">
-        <v>5.494890839889778</v>
+        <v>5.91757475065053</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05055598659316449</v>
+        <v>0.04997488329899018</v>
       </c>
       <c r="W88">
-        <v>0.2238788983613318</v>
+        <v>0.2240159225180981</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2022239463726581</v>
+        <v>0.1998995331959607</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2537152272057131</v>
+        <v>0.2556152272057131</v>
       </c>
       <c r="C89">
-        <v>-20.95764929553095</v>
+        <v>-21.40259103346069</v>
       </c>
       <c r="D89">
-        <v>9.280650704469052</v>
+        <v>9.196608966539316</v>
       </c>
       <c r="E89">
-        <v>30.9083</v>
+        <v>31.2692</v>
       </c>
       <c r="F89">
-        <v>31.3983</v>
+        <v>31.7592</v>
       </c>
       <c r="G89">
         <v>1.16</v>
@@ -8579,37 +8579,37 @@
         <v>1.48</v>
       </c>
       <c r="M89">
-        <v>7.403719140000001</v>
+        <v>7.488819360000001</v>
       </c>
       <c r="N89">
-        <v>-5.923719140000001</v>
+        <v>-6.00881936</v>
       </c>
       <c r="O89">
-        <v>-1.480929785</v>
+        <v>-1.50220484</v>
       </c>
       <c r="P89">
-        <v>-4.442789355</v>
+        <v>-4.50661452</v>
       </c>
       <c r="Q89">
-        <v>-3.902789355</v>
+        <v>-3.96661452</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4524721124228285</v>
+        <v>0.4863614551247309</v>
       </c>
       <c r="T89">
-        <v>5.91757475065053</v>
+        <v>6.410705979871409</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04997488329899018</v>
+        <v>0.0494069868978653</v>
       </c>
       <c r="W89">
-        <v>0.2240159225180981</v>
+        <v>0.2241498324894834</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1998995331959607</v>
+        <v>0.1976279475914612</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2556152272057131</v>
+        <v>0.2575152272057131</v>
       </c>
       <c r="C90">
-        <v>-21.40259103346069</v>
+        <v>-21.8460243366484</v>
       </c>
       <c r="D90">
-        <v>9.196608966539316</v>
+        <v>9.114075663351601</v>
       </c>
       <c r="E90">
-        <v>31.2692</v>
+        <v>31.6301</v>
       </c>
       <c r="F90">
-        <v>31.7592</v>
+        <v>32.1201</v>
       </c>
       <c r="G90">
         <v>1.16</v>
@@ -8661,37 +8661,37 @@
         <v>1.48</v>
       </c>
       <c r="M90">
-        <v>7.488819360000001</v>
+        <v>7.57391958</v>
       </c>
       <c r="N90">
-        <v>-6.00881936</v>
+        <v>-6.09391958</v>
       </c>
       <c r="O90">
-        <v>-1.50220484</v>
+        <v>-1.523479895</v>
       </c>
       <c r="P90">
-        <v>-4.50661452</v>
+        <v>-4.570439685</v>
       </c>
       <c r="Q90">
-        <v>-3.96661452</v>
+        <v>-4.030439685</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4863614551247309</v>
+        <v>0.5264124964997065</v>
       </c>
       <c r="T90">
-        <v>6.410705979871409</v>
+        <v>6.993497432586992</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0494069868978653</v>
+        <v>0.04885185221361962</v>
       </c>
       <c r="W90">
-        <v>0.2241498324894834</v>
+        <v>0.2242807332480285</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1976279475914612</v>
+        <v>0.1954074088544785</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2575152272057131</v>
+        <v>0.2594152272057131</v>
       </c>
       <c r="C91">
-        <v>-21.8460243366484</v>
+        <v>-22.287989455399</v>
       </c>
       <c r="D91">
-        <v>9.114075663351601</v>
+        <v>9.033010544600998</v>
       </c>
       <c r="E91">
-        <v>31.6301</v>
+        <v>31.991</v>
       </c>
       <c r="F91">
-        <v>32.1201</v>
+        <v>32.481</v>
       </c>
       <c r="G91">
         <v>1.16</v>
@@ -8743,37 +8743,37 @@
         <v>1.48</v>
       </c>
       <c r="M91">
-        <v>7.57391958</v>
+        <v>7.6590198</v>
       </c>
       <c r="N91">
-        <v>-6.09391958</v>
+        <v>-6.179019800000001</v>
       </c>
       <c r="O91">
-        <v>-1.523479895</v>
+        <v>-1.54475495</v>
       </c>
       <c r="P91">
-        <v>-4.570439685</v>
+        <v>-4.634264850000001</v>
       </c>
       <c r="Q91">
-        <v>-4.030439685</v>
+        <v>-4.094264850000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5264124964997065</v>
+        <v>0.5744737461496771</v>
       </c>
       <c r="T91">
-        <v>6.993497432586992</v>
+        <v>7.69284717584569</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04885185221361962</v>
+        <v>0.04830905385569052</v>
       </c>
       <c r="W91">
-        <v>0.2242807332480285</v>
+        <v>0.2244087251008282</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1954074088544785</v>
+        <v>0.193236215422762</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2594152272057131</v>
+        <v>0.2613152272057131</v>
       </c>
       <c r="C92">
-        <v>-22.287989455399</v>
+        <v>-22.72852522061739</v>
       </c>
       <c r="D92">
-        <v>9.033010544600998</v>
+        <v>8.95337477938261</v>
       </c>
       <c r="E92">
-        <v>31.991</v>
+        <v>32.3519</v>
       </c>
       <c r="F92">
-        <v>32.481</v>
+        <v>32.8419</v>
       </c>
       <c r="G92">
         <v>1.16</v>
@@ -8825,37 +8825,37 @@
         <v>1.48</v>
       </c>
       <c r="M92">
-        <v>7.6590198</v>
+        <v>7.744120020000001</v>
       </c>
       <c r="N92">
-        <v>-6.179019800000001</v>
+        <v>-6.264120020000002</v>
       </c>
       <c r="O92">
-        <v>-1.54475495</v>
+        <v>-1.566030005</v>
       </c>
       <c r="P92">
-        <v>-4.634264850000001</v>
+        <v>-4.698090015000002</v>
       </c>
       <c r="Q92">
-        <v>-4.094264850000001</v>
+        <v>-4.158090015000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5744737461496771</v>
+        <v>0.6332152734996414</v>
       </c>
       <c r="T92">
-        <v>7.69284717584569</v>
+        <v>8.547607973161881</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04830905385569052</v>
+        <v>0.0477781851320016</v>
       </c>
       <c r="W92">
-        <v>0.2244087251008282</v>
+        <v>0.224533903945874</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.193236215422762</v>
+        <v>0.1911127405280063</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2613152272057131</v>
+        <v>0.2632152272057131</v>
       </c>
       <c r="C93">
-        <v>-22.72852522061739</v>
+        <v>-23.1676691058294</v>
       </c>
       <c r="D93">
-        <v>8.95337477938261</v>
+        <v>8.875130894170603</v>
       </c>
       <c r="E93">
-        <v>32.3519</v>
+        <v>32.7128</v>
       </c>
       <c r="F93">
-        <v>32.8419</v>
+        <v>33.2028</v>
       </c>
       <c r="G93">
         <v>1.16</v>
@@ -8907,37 +8907,37 @@
         <v>1.48</v>
       </c>
       <c r="M93">
-        <v>7.744120020000001</v>
+        <v>7.829220240000001</v>
       </c>
       <c r="N93">
-        <v>-6.264120020000002</v>
+        <v>-6.349220240000001</v>
       </c>
       <c r="O93">
-        <v>-1.566030005</v>
+        <v>-1.58730506</v>
       </c>
       <c r="P93">
-        <v>-4.698090015000002</v>
+        <v>-4.761915180000001</v>
       </c>
       <c r="Q93">
-        <v>-4.158090015000002</v>
+        <v>-4.221915180000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6332152734996414</v>
+        <v>0.7066421826870967</v>
       </c>
       <c r="T93">
-        <v>8.547607973161881</v>
+        <v>9.616058969807117</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0477781851320016</v>
+        <v>0.04725885703274071</v>
       </c>
       <c r="W93">
-        <v>0.224533903945874</v>
+        <v>0.2246563615116798</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1911127405280063</v>
+        <v>0.1890354281309629</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2632152272057131</v>
+        <v>0.2651152272057131</v>
       </c>
       <c r="C94">
-        <v>-23.1676691058294</v>
+        <v>-23.60545728597891</v>
       </c>
       <c r="D94">
-        <v>8.875130894170603</v>
+        <v>8.798242714021088</v>
       </c>
       <c r="E94">
-        <v>32.7128</v>
+        <v>33.0737</v>
       </c>
       <c r="F94">
-        <v>33.2028</v>
+        <v>33.5637</v>
       </c>
       <c r="G94">
         <v>1.16</v>
@@ -8989,37 +8989,37 @@
         <v>1.48</v>
       </c>
       <c r="M94">
-        <v>7.829220240000001</v>
+        <v>7.914320460000002</v>
       </c>
       <c r="N94">
-        <v>-6.349220240000001</v>
+        <v>-6.434320460000002</v>
       </c>
       <c r="O94">
-        <v>-1.58730506</v>
+        <v>-1.608580115000001</v>
       </c>
       <c r="P94">
-        <v>-4.761915180000001</v>
+        <v>-4.825740345000002</v>
       </c>
       <c r="Q94">
-        <v>-4.221915180000001</v>
+        <v>-4.285740345000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7066421826870967</v>
+        <v>0.8010482087852534</v>
       </c>
       <c r="T94">
-        <v>9.616058969807117</v>
+        <v>10.98978167977956</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04725885703274071</v>
+        <v>0.04675069727970049</v>
       </c>
       <c r="W94">
-        <v>0.2246563615116798</v>
+        <v>0.2247761855814466</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1890354281309629</v>
+        <v>0.1870027891188019</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2651152272057131</v>
+        <v>0.2670152272057131</v>
       </c>
       <c r="C95">
-        <v>-23.60545728597891</v>
+        <v>-24.04192469319494</v>
       </c>
       <c r="D95">
-        <v>8.798242714021088</v>
+        <v>8.72267530680506</v>
       </c>
       <c r="E95">
-        <v>33.0737</v>
+        <v>33.4346</v>
       </c>
       <c r="F95">
-        <v>33.5637</v>
+        <v>33.92460000000001</v>
       </c>
       <c r="G95">
         <v>1.16</v>
@@ -9071,37 +9071,37 @@
         <v>1.48</v>
       </c>
       <c r="M95">
-        <v>7.914320460000002</v>
+        <v>7.999420680000002</v>
       </c>
       <c r="N95">
-        <v>-6.434320460000002</v>
+        <v>-6.519420680000001</v>
       </c>
       <c r="O95">
-        <v>-1.608580115000001</v>
+        <v>-1.62985517</v>
       </c>
       <c r="P95">
-        <v>-4.825740345000002</v>
+        <v>-4.889565510000001</v>
       </c>
       <c r="Q95">
-        <v>-4.285740345000002</v>
+        <v>-4.349565510000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8010482087852534</v>
+        <v>0.9269229102494625</v>
       </c>
       <c r="T95">
-        <v>10.98978167977956</v>
+        <v>12.82141195974283</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04675069727970049</v>
+        <v>0.04625334943629942</v>
       </c>
       <c r="W95">
-        <v>0.2247761855814466</v>
+        <v>0.2248934602029206</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1870027891188019</v>
+        <v>0.1850133977451978</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2670152272057131</v>
+        <v>0.2689152272057131</v>
       </c>
       <c r="C96">
-        <v>-24.04192469319494</v>
+        <v>-24.47710506970932</v>
       </c>
       <c r="D96">
-        <v>8.72267530680506</v>
+        <v>8.64839493029069</v>
       </c>
       <c r="E96">
-        <v>33.4346</v>
+        <v>33.7955</v>
       </c>
       <c r="F96">
-        <v>33.92460000000001</v>
+        <v>34.28550000000001</v>
       </c>
       <c r="G96">
         <v>1.16</v>
@@ -9153,37 +9153,37 @@
         <v>1.48</v>
       </c>
       <c r="M96">
-        <v>7.999420680000002</v>
+        <v>8.084520900000001</v>
       </c>
       <c r="N96">
-        <v>-6.519420680000001</v>
+        <v>-6.604520900000001</v>
       </c>
       <c r="O96">
-        <v>-1.62985517</v>
+        <v>-1.651130225</v>
       </c>
       <c r="P96">
-        <v>-4.889565510000001</v>
+        <v>-4.953390675000001</v>
       </c>
       <c r="Q96">
-        <v>-4.349565510000001</v>
+        <v>-4.413390675</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9269229102494625</v>
+        <v>1.103147492299356</v>
       </c>
       <c r="T96">
-        <v>12.82141195974283</v>
+        <v>15.3856943516914</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04625334943629942</v>
+        <v>0.04576647207381206</v>
       </c>
       <c r="W96">
-        <v>0.2248934602029206</v>
+        <v>0.2250082658849951</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1850133977451978</v>
+        <v>0.1830658882952483</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2689152272057131</v>
+        <v>0.2708152272057131</v>
       </c>
       <c r="C97">
-        <v>-24.47710506970932</v>
+        <v>-24.91103101809338</v>
       </c>
       <c r="D97">
-        <v>8.64839493029069</v>
+        <v>8.575368981906628</v>
       </c>
       <c r="E97">
-        <v>33.7955</v>
+        <v>34.1564</v>
       </c>
       <c r="F97">
-        <v>34.28550000000001</v>
+        <v>34.64640000000001</v>
       </c>
       <c r="G97">
         <v>1.16</v>
@@ -9235,37 +9235,37 @@
         <v>1.48</v>
       </c>
       <c r="M97">
-        <v>8.084520900000001</v>
+        <v>8.169621120000002</v>
       </c>
       <c r="N97">
-        <v>-6.604520900000001</v>
+        <v>-6.689621120000002</v>
       </c>
       <c r="O97">
-        <v>-1.651130225</v>
+        <v>-1.67240528</v>
       </c>
       <c r="P97">
-        <v>-4.953390675000001</v>
+        <v>-5.017215840000001</v>
       </c>
       <c r="Q97">
-        <v>-4.413390675</v>
+        <v>-4.477215840000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.103147492299356</v>
+        <v>1.367484365374195</v>
       </c>
       <c r="T97">
-        <v>15.3856943516914</v>
+        <v>19.23211793961426</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04576647207381206</v>
+        <v>0.04528973798970985</v>
       </c>
       <c r="W97">
-        <v>0.2250082658849951</v>
+        <v>0.2251206797820264</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1830658882952483</v>
+        <v>0.1811589519588395</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2708152272057131</v>
+        <v>0.2727152272057131</v>
       </c>
       <c r="C98">
-        <v>-24.91103101809337</v>
+        <v>-25.34373404897085</v>
       </c>
       <c r="D98">
-        <v>8.575368981906628</v>
+        <v>8.503565951029149</v>
       </c>
       <c r="E98">
-        <v>34.1564</v>
+        <v>34.5173</v>
       </c>
       <c r="F98">
-        <v>34.6464</v>
+        <v>35.0073</v>
       </c>
       <c r="G98">
         <v>1.16</v>
@@ -9317,37 +9317,37 @@
         <v>1.48</v>
       </c>
       <c r="M98">
-        <v>8.16962112</v>
+        <v>8.25472134</v>
       </c>
       <c r="N98">
-        <v>-6.68962112</v>
+        <v>-6.774721339999999</v>
       </c>
       <c r="O98">
-        <v>-1.67240528</v>
+        <v>-1.693680335</v>
       </c>
       <c r="P98">
-        <v>-5.01721584</v>
+        <v>-5.081041004999999</v>
       </c>
       <c r="Q98">
-        <v>-4.47721584</v>
+        <v>-4.541041004999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.367484365374192</v>
+        <v>1.808045820498922</v>
       </c>
       <c r="T98">
-        <v>19.23211793961421</v>
+        <v>25.64282391948561</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04528973798970985</v>
+        <v>0.04482283347435202</v>
       </c>
       <c r="W98">
-        <v>0.2251206797820264</v>
+        <v>0.2252307758667478</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1811589519588395</v>
+        <v>0.1792913338974081</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2727152272057131</v>
+        <v>0.2746152272057131</v>
       </c>
       <c r="C99">
-        <v>-25.34373404897085</v>
+        <v>-25.77524462635358</v>
       </c>
       <c r="D99">
-        <v>8.503565951029149</v>
+        <v>8.432955373646418</v>
       </c>
       <c r="E99">
-        <v>34.5173</v>
+        <v>34.8782</v>
       </c>
       <c r="F99">
-        <v>35.0073</v>
+        <v>35.3682</v>
       </c>
       <c r="G99">
         <v>1.16</v>
@@ -9399,37 +9399,37 @@
         <v>1.48</v>
       </c>
       <c r="M99">
-        <v>8.25472134</v>
+        <v>8.339821560000001</v>
       </c>
       <c r="N99">
-        <v>-6.774721339999999</v>
+        <v>-6.85982156</v>
       </c>
       <c r="O99">
-        <v>-1.693680335</v>
+        <v>-1.71495539</v>
       </c>
       <c r="P99">
-        <v>-5.081041004999999</v>
+        <v>-5.14486617</v>
       </c>
       <c r="Q99">
-        <v>-4.541041004999999</v>
+        <v>-4.60486617</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.808045820498922</v>
+        <v>2.689168730748383</v>
       </c>
       <c r="T99">
-        <v>25.64282391948561</v>
+        <v>38.46423587922841</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04482283347435202</v>
+        <v>0.04436545762257292</v>
       </c>
       <c r="W99">
-        <v>0.2252307758667478</v>
+        <v>0.2253386250925973</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1792913338974081</v>
+        <v>0.1774618304902917</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2746152272057131</v>
+        <v>0.2765152272057131</v>
       </c>
       <c r="C100">
-        <v>-25.77524462635358</v>
+        <v>-26.20559221073709</v>
       </c>
       <c r="D100">
-        <v>8.432955373646418</v>
+        <v>8.363507789262917</v>
       </c>
       <c r="E100">
-        <v>34.8782</v>
+        <v>35.2391</v>
       </c>
       <c r="F100">
-        <v>35.3682</v>
+        <v>35.7291</v>
       </c>
       <c r="G100">
         <v>1.16</v>
@@ -9481,37 +9481,37 @@
         <v>1.48</v>
       </c>
       <c r="M100">
-        <v>8.339821560000001</v>
+        <v>8.424921780000002</v>
       </c>
       <c r="N100">
-        <v>-6.85982156</v>
+        <v>-6.944921780000001</v>
       </c>
       <c r="O100">
-        <v>-1.71495539</v>
+        <v>-1.736230445</v>
       </c>
       <c r="P100">
-        <v>-5.14486617</v>
+        <v>-5.208691335000001</v>
       </c>
       <c r="Q100">
-        <v>-4.60486617</v>
+        <v>-4.668691335000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.689168730748383</v>
+        <v>5.332537461496766</v>
       </c>
       <c r="T100">
-        <v>38.46423587922841</v>
+        <v>76.92847175845682</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04436545762257292</v>
+        <v>0.04391732168699137</v>
       </c>
       <c r="W100">
-        <v>0.2253386250925973</v>
+        <v>0.2254442955462075</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1774618304902917</v>
+        <v>0.1756692867479656</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2765152272057131</v>
-      </c>
-      <c r="C101">
-        <v>-26.20559221073709</v>
-      </c>
-      <c r="D101">
-        <v>8.363507789262917</v>
-      </c>
-      <c r="E101">
-        <v>35.2391</v>
-      </c>
-      <c r="F101">
-        <v>35.7291</v>
-      </c>
-      <c r="G101">
-        <v>1.16</v>
-      </c>
-      <c r="H101">
-        <v>35.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.02</v>
-      </c>
-      <c r="K101">
-        <v>0.54</v>
-      </c>
-      <c r="L101">
-        <v>1.48</v>
-      </c>
-      <c r="M101">
-        <v>8.424921780000002</v>
-      </c>
-      <c r="N101">
-        <v>-6.944921780000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.736230445</v>
-      </c>
-      <c r="P101">
-        <v>-5.208691335000001</v>
-      </c>
-      <c r="Q101">
-        <v>-4.668691335000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.332537461496766</v>
-      </c>
-      <c r="T101">
-        <v>76.92847175845682</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04391732168699137</v>
-      </c>
-      <c r="W101">
-        <v>0.2254442955462075</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1756692867479656</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
